--- a/results/enrichment_OR_by_protein_class.xlsx
+++ b/results/enrichment_OR_by_protein_class.xlsx
@@ -992,7 +992,7 @@
         <v>1.414291161765952</v>
       </c>
       <c r="V2" t="n">
-        <v>2.152166246422243</v>
+        <v>2.410680228862047</v>
       </c>
     </row>
     <row r="3">
@@ -1062,7 +1062,7 @@
         <v>1.171341960069252</v>
       </c>
       <c r="V3" t="n">
-        <v>2.737234015384066</v>
+        <v>3.004712795224284</v>
       </c>
     </row>
     <row r="4">
@@ -1132,7 +1132,7 @@
         <v>1.599484995543231</v>
       </c>
       <c r="V4" t="n">
-        <v>1.381683612527267</v>
+        <v>1.528963706422324</v>
       </c>
     </row>
     <row r="5">
@@ -1202,7 +1202,7 @@
         <v>2.308838444689115</v>
       </c>
       <c r="V5" t="n">
-        <v>1.746340613717427</v>
+        <v>1.652671342585061</v>
       </c>
     </row>
     <row r="6">
@@ -1272,7 +1272,7 @@
         <v>2.976705674541841</v>
       </c>
       <c r="V6" t="n">
-        <v>4.263884641312748</v>
+        <v>3.396276720695325</v>
       </c>
     </row>
     <row r="7">
@@ -1342,7 +1342,7 @@
         <v>0.4504727266188021</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5950950864601613</v>
+        <v>0.6553614106434607</v>
       </c>
     </row>
     <row r="8">
@@ -1412,7 +1412,7 @@
         <v>0.2376281307478326</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2839449001312492</v>
+        <v>0.2903015530752545</v>
       </c>
     </row>
     <row r="9">
@@ -1482,7 +1482,7 @@
         <v>1.133430803389811</v>
       </c>
       <c r="V9" t="n">
-        <v>1.689364056383284</v>
+        <v>1.623589379429703</v>
       </c>
     </row>
     <row r="10">
@@ -1552,7 +1552,7 @@
         <v>1.156380112662258</v>
       </c>
       <c r="V10" t="n">
-        <v>1.357231805907464</v>
+        <v>1.320652155716776</v>
       </c>
     </row>
     <row r="11">
@@ -1622,7 +1622,7 @@
         <v>6.139804309318023</v>
       </c>
       <c r="V11" t="n">
-        <v>7.783866251407107</v>
+        <v>8.614183689716173</v>
       </c>
     </row>
     <row r="12">
@@ -1692,7 +1692,7 @@
         <v>2.720441206606828</v>
       </c>
       <c r="V12" t="n">
-        <v>3.121528951201924</v>
+        <v>3.151029808311762</v>
       </c>
     </row>
     <row r="13">
@@ -1762,7 +1762,7 @@
         <v>0.8055461473588879</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9873583099082808</v>
+        <v>0.9317932571710792</v>
       </c>
     </row>
     <row r="14">
@@ -1832,7 +1832,7 @@
         <v>0.1953297429569747</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2508071409445737</v>
+        <v>0.2387492071285908</v>
       </c>
     </row>
     <row r="15">
@@ -1842,67 +1842,67 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1408640391126701</v>
+        <v>0.2006866242123425</v>
       </c>
       <c r="C15" t="n">
-        <v>0.12273052832964</v>
+        <v>0.2135420681385774</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3036283168959005</v>
+        <v>0.4024412351199468</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1034384498480243</v>
+        <v>0.1965854043149751</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2415661566156616</v>
+        <v>0.2677041602465332</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1269053793712013</v>
+        <v>0.1574338459798711</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2692142123911388</v>
+        <v>0.4531671441255801</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1646527612047158</v>
+        <v>0.1775834866789343</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1575449246343128</v>
+        <v>0.1903733612587032</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2542922095548317</v>
+        <v>0.3727135459128019</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1779084158415841</v>
+        <v>0.2941382785728684</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1266222012149222</v>
+        <v>0.2885198058116895</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1765721447228176</v>
+        <v>0.2396036348674364</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1388210292805538</v>
+        <v>0.1922320870695632</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1652864464040311</v>
+        <v>0.2751287744009724</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1216940409936202</v>
+        <v>0.1624608967674661</v>
       </c>
       <c r="R15" t="n">
-        <v>0.09382499268364063</v>
+        <v>0.1514454472796741</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1369179600886918</v>
+        <v>0.3065615756438929</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1521445279484563</v>
+        <v>0.2021646316068252</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08867924314023438</v>
+        <v>0.1222775900900901</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1571778277633257</v>
+        <v>0.2406747804856074</v>
       </c>
     </row>
     <row r="16">
@@ -1972,7 +1972,7 @@
         <v>0.06294008897063386</v>
       </c>
       <c r="V16" t="n">
-        <v>0.112618117972902</v>
+        <v>0.1161404331975514</v>
       </c>
     </row>
     <row r="17">
@@ -2042,7 +2042,7 @@
         <v>0.5877224273645693</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5695702917771883</v>
+        <v>0.535232491621727</v>
       </c>
     </row>
     <row r="18">
@@ -2112,7 +2112,7 @@
         <v>1.946553496477175</v>
       </c>
       <c r="V18" t="n">
-        <v>1.498783727107507</v>
+        <v>1.505901955354574</v>
       </c>
     </row>
     <row r="19">
@@ -2182,7 +2182,7 @@
         <v>2.623073691219837</v>
       </c>
       <c r="V19" t="n">
-        <v>4.683348883992085</v>
+        <v>4.890492051569368</v>
       </c>
     </row>
     <row r="20">
@@ -2252,7 +2252,7 @@
         <v>0.3665500612999313</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3759522609858034</v>
+        <v>0.3540305544871876</v>
       </c>
     </row>
     <row r="21">
@@ -2322,7 +2322,7 @@
         <v>1.556127506305634</v>
       </c>
       <c r="V21" t="n">
-        <v>1.425284168219213</v>
+        <v>1.389450978670143</v>
       </c>
     </row>
     <row r="22">
@@ -2392,7 +2392,7 @@
         <v>0.7426457066700033</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7027798952540445</v>
+        <v>0.7115584755914944</v>
       </c>
     </row>
     <row r="23">
@@ -2462,7 +2462,7 @@
         <v>7.240541944420396</v>
       </c>
       <c r="V23" t="n">
-        <v>7.450821079201745</v>
+        <v>7.626990183138096</v>
       </c>
     </row>
     <row r="24">
@@ -2532,7 +2532,7 @@
         <v>4.112371665190222</v>
       </c>
       <c r="V24" t="n">
-        <v>4.069377442914696</v>
+        <v>4.105070395738204</v>
       </c>
     </row>
     <row r="25">
@@ -2602,7 +2602,7 @@
         <v>4.062894208170637</v>
       </c>
       <c r="V25" t="n">
-        <v>3.520709880535684</v>
+        <v>3.592350455279597</v>
       </c>
     </row>
     <row r="26">
@@ -2672,7 +2672,7 @@
         <v>1.481583609534816</v>
       </c>
       <c r="V26" t="n">
-        <v>1.701857783541382</v>
+        <v>1.570236248343174</v>
       </c>
     </row>
     <row r="27">
@@ -2742,7 +2742,7 @@
         <v>1.643018246476604</v>
       </c>
       <c r="V27" t="n">
-        <v>0.8417424369201019</v>
+        <v>0.849854748603352</v>
       </c>
     </row>
     <row r="28">
@@ -2812,7 +2812,7 @@
         <v>8.823883791369518</v>
       </c>
       <c r="V28" t="n">
-        <v>5.502537235352043</v>
+        <v>5.411370188289549</v>
       </c>
     </row>
     <row r="29">
@@ -2882,7 +2882,7 @@
         <v>2.744387743320941</v>
       </c>
       <c r="V29" t="n">
-        <v>3.046183203797129</v>
+        <v>2.923843806770696</v>
       </c>
     </row>
     <row r="30">
@@ -2956,7 +2956,7 @@
         <v>20.18490345231129</v>
       </c>
       <c r="V30" t="n">
-        <v>7.109056795869392</v>
+        <v>7.111484593837535</v>
       </c>
     </row>
     <row r="31">
@@ -3026,7 +3026,7 @@
         <v>2.907918153568102</v>
       </c>
       <c r="V31" t="n">
-        <v>3.338169232769802</v>
+        <v>3.418802969378286</v>
       </c>
     </row>
     <row r="32">
@@ -3096,7 +3096,7 @@
         <v>0.5460042217003904</v>
       </c>
       <c r="V32" t="n">
-        <v>0.3815272858148977</v>
+        <v>0.3728677187469709</v>
       </c>
     </row>
     <row r="33">
@@ -3166,7 +3166,7 @@
         <v>2.713617738480679</v>
       </c>
       <c r="V33" t="n">
-        <v>1.690090980050724</v>
+        <v>1.581636999933544</v>
       </c>
     </row>
     <row r="34">
@@ -3236,7 +3236,7 @@
         <v>0.4910251632802471</v>
       </c>
       <c r="V34" t="n">
-        <v>0.3221955533075198</v>
+        <v>0.312988988074982</v>
       </c>
     </row>
     <row r="35">
@@ -3306,7 +3306,7 @@
         <v>1.478563398311628</v>
       </c>
       <c r="V35" t="n">
-        <v>1.058180986160391</v>
+        <v>1.070692748698659</v>
       </c>
     </row>
     <row r="36">
@@ -3376,7 +3376,7 @@
         <v>0.9428212099797578</v>
       </c>
       <c r="V36" t="n">
-        <v>0.6528976889011074</v>
+        <v>0.6491895033689966</v>
       </c>
     </row>
     <row r="37">
@@ -3446,7 +3446,7 @@
         <v>1.5299450343486</v>
       </c>
       <c r="V37" t="n">
-        <v>1.134194393092857</v>
+        <v>1.128180937005272</v>
       </c>
     </row>
     <row r="38">
@@ -3516,7 +3516,7 @@
         <v>2.266133806178817</v>
       </c>
       <c r="V38" t="n">
-        <v>2.451651144755752</v>
+        <v>2.469265776455511</v>
       </c>
     </row>
     <row r="39">
@@ -3586,7 +3586,7 @@
         <v>0.4022091030279947</v>
       </c>
       <c r="V39" t="n">
-        <v>0.6904254443385178</v>
+        <v>0.7073184949944156</v>
       </c>
     </row>
     <row r="40">
@@ -3656,7 +3656,7 @@
         <v>0.4480208478285621</v>
       </c>
       <c r="V40" t="n">
-        <v>0.4434779550118076</v>
+        <v>0.4602638996062065</v>
       </c>
     </row>
     <row r="41">
@@ -3726,7 +3726,7 @@
         <v>0.2446701305018558</v>
       </c>
       <c r="V41" t="n">
-        <v>0.3134931920147949</v>
+        <v>0.3198164945332604</v>
       </c>
     </row>
     <row r="42">
@@ -3796,7 +3796,7 @@
         <v>1.144580179796042</v>
       </c>
       <c r="V42" t="n">
-        <v>1.340418143717892</v>
+        <v>1.29363368073442</v>
       </c>
     </row>
     <row r="43">
@@ -3866,7 +3866,7 @@
         <v>0.9890585128789636</v>
       </c>
       <c r="V43" t="n">
-        <v>1.420778810646588</v>
+        <v>1.440042287139589</v>
       </c>
     </row>
     <row r="44">
@@ -3936,7 +3936,7 @@
         <v>3.325312038526294</v>
       </c>
       <c r="V44" t="n">
-        <v>2.076729814649645</v>
+        <v>2.018295074117341</v>
       </c>
     </row>
     <row r="45">
@@ -4006,7 +4006,7 @@
         <v>4.767835570469798</v>
       </c>
       <c r="V45" t="n">
-        <v>5.031857017671973</v>
+        <v>5.019860907663275</v>
       </c>
     </row>
     <row r="46">
@@ -4076,7 +4076,7 @@
         <v>0.7438717212653383</v>
       </c>
       <c r="V46" t="n">
-        <v>0.7418369565263634</v>
+        <v>0.7347101910308488</v>
       </c>
     </row>
     <row r="47">
@@ -4146,7 +4146,7 @@
         <v>1.08847540625022</v>
       </c>
       <c r="V47" t="n">
-        <v>1.060356471712013</v>
+        <v>1.03716135313074</v>
       </c>
     </row>
     <row r="48">
@@ -4216,7 +4216,7 @@
         <v>0.7038407285505704</v>
       </c>
       <c r="V48" t="n">
-        <v>0.5617722061467144</v>
+        <v>0.5536809605958543</v>
       </c>
     </row>
     <row r="49">
@@ -4286,7 +4286,7 @@
         <v>1.635570050875223</v>
       </c>
       <c r="V49" t="n">
-        <v>1.572556094956337</v>
+        <v>1.528274293142671</v>
       </c>
     </row>
     <row r="50">
@@ -4356,7 +4356,7 @@
         <v>1.121846819733847</v>
       </c>
       <c r="V50" t="n">
-        <v>1.031029429388623</v>
+        <v>1.047621057574539</v>
       </c>
     </row>
     <row r="51">
@@ -4426,7 +4426,7 @@
         <v>3.440196036861149</v>
       </c>
       <c r="V51" t="n">
-        <v>7.453523473263483</v>
+        <v>7.875072728783975</v>
       </c>
     </row>
     <row r="52">
@@ -4496,7 +4496,7 @@
         <v>0.6737708464695272</v>
       </c>
       <c r="V52" t="n">
-        <v>0.8356742333968881</v>
+        <v>0.8275478175354586</v>
       </c>
     </row>
     <row r="53">
@@ -4566,7 +4566,7 @@
         <v>2.00694579052788</v>
       </c>
       <c r="V53" t="n">
-        <v>2.196406281492977</v>
+        <v>2.2297260538335</v>
       </c>
     </row>
     <row r="54">
@@ -4636,7 +4636,7 @@
         <v>2.667525802395006</v>
       </c>
       <c r="V54" t="n">
-        <v>2.215337673043384</v>
+        <v>2.250379569714546</v>
       </c>
     </row>
     <row r="55">
@@ -4706,7 +4706,7 @@
         <v>4.619922341696535</v>
       </c>
       <c r="V55" t="n">
-        <v>7.813989220318961</v>
+        <v>8.191333799573675</v>
       </c>
     </row>
     <row r="56">
@@ -4776,7 +4776,7 @@
         <v>0.8569081445212191</v>
       </c>
       <c r="V56" t="n">
-        <v>0.881263892631425</v>
+        <v>0.8718455702733591</v>
       </c>
     </row>
     <row r="57">
@@ -4846,7 +4846,7 @@
         <v>2.93984645554696</v>
       </c>
       <c r="V57" t="n">
-        <v>3.047387490340196</v>
+        <v>2.997948325625065</v>
       </c>
     </row>
     <row r="58">
@@ -4916,7 +4916,7 @@
         <v>0.9034723549439737</v>
       </c>
       <c r="V58" t="n">
-        <v>0.6117384456487518</v>
+        <v>0.6029513182689548</v>
       </c>
     </row>
     <row r="59">
@@ -4986,7 +4986,7 @@
         <v>0.5159995984475464</v>
       </c>
       <c r="V59" t="n">
-        <v>0.6331194141829067</v>
+        <v>0.646821235600442</v>
       </c>
     </row>
     <row r="60">
@@ -5056,7 +5056,7 @@
         <v>1.258014190521423</v>
       </c>
       <c r="V60" t="n">
-        <v>1.121814712005552</v>
+        <v>1.099759710595127</v>
       </c>
     </row>
     <row r="61">
@@ -5126,7 +5126,7 @@
         <v>1.527064387661474</v>
       </c>
       <c r="V61" t="n">
-        <v>1.802041643100661</v>
+        <v>1.84855505142119</v>
       </c>
     </row>
     <row r="62">
@@ -5196,7 +5196,7 @@
         <v>0.4027719220932309</v>
       </c>
       <c r="V62" t="n">
-        <v>0.3841717293371693</v>
+        <v>0.3735177086763597</v>
       </c>
     </row>
     <row r="63">
@@ -5266,7 +5266,7 @@
         <v>0.9721070736690298</v>
       </c>
       <c r="V63" t="n">
-        <v>0.8642825590441949</v>
+        <v>0.8616258949698263</v>
       </c>
     </row>
     <row r="64">
@@ -5336,7 +5336,7 @@
         <v>2.667170582084834</v>
       </c>
       <c r="V64" t="n">
-        <v>2.395220678376682</v>
+        <v>2.409361054179306</v>
       </c>
     </row>
     <row r="65">
@@ -5406,7 +5406,7 @@
         <v>2.355509404974745</v>
       </c>
       <c r="V65" t="n">
-        <v>3.406428817848355</v>
+        <v>3.491145719720989</v>
       </c>
     </row>
     <row r="66">
@@ -5476,7 +5476,7 @@
         <v>5.553634208906844</v>
       </c>
       <c r="V66" t="n">
-        <v>3.58351681182787</v>
+        <v>3.457555489492938</v>
       </c>
     </row>
     <row r="67">
@@ -5546,7 +5546,7 @@
         <v>2.609540375025436</v>
       </c>
       <c r="V67" t="n">
-        <v>1.875174103106334</v>
+        <v>1.895130036055401</v>
       </c>
     </row>
     <row r="68">
@@ -5626,7 +5626,7 @@
         <v>65.07251236482522</v>
       </c>
       <c r="V68" t="n">
-        <v>261.7456212988056</v>
+        <v>318.7997675769901</v>
       </c>
     </row>
     <row r="69">
@@ -5696,7 +5696,7 @@
         <v>7.021055836689845</v>
       </c>
       <c r="V69" t="n">
-        <v>3.804252280136142</v>
+        <v>3.622456710513598</v>
       </c>
     </row>
     <row r="70">
@@ -5748,7 +5748,7 @@
         </is>
       </c>
       <c r="V70" t="n">
-        <v>97.32404383482111</v>
+        <v>94.34944089456869</v>
       </c>
     </row>
     <row r="71">
@@ -5828,7 +5828,7 @@
         <v>6.416206034979819</v>
       </c>
       <c r="V71" t="n">
-        <v>40.18891925832902</v>
+        <v>36.53006970335549</v>
       </c>
     </row>
     <row r="72">
@@ -5892,7 +5892,7 @@
         <v>2.872657616390439</v>
       </c>
       <c r="V72" t="n">
-        <v>5.71577650554388</v>
+        <v>6.077849565286751</v>
       </c>
     </row>
     <row r="73">
@@ -5936,7 +5936,7 @@
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="n">
-        <v>3.248212557921366</v>
+        <v>3.454589452351064</v>
       </c>
     </row>
     <row r="74">
@@ -5992,7 +5992,7 @@
         <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>4.849902861208223</v>
+        <v>5.126595442815689</v>
       </c>
     </row>
     <row r="75">
@@ -6062,7 +6062,7 @@
         <v>0.05901116818192603</v>
       </c>
       <c r="V75" t="n">
-        <v>0.09461128165699292</v>
+        <v>0.1008894646671185</v>
       </c>
     </row>
     <row r="76">
@@ -6132,7 +6132,7 @@
         <v>4.611801564003256</v>
       </c>
       <c r="V76" t="n">
-        <v>1.585844023271312</v>
+        <v>1.473274809956918</v>
       </c>
     </row>
     <row r="77">
@@ -6202,7 +6202,7 @@
         <v>0.6219136574940586</v>
       </c>
       <c r="V77" t="n">
-        <v>1.960033420247939</v>
+        <v>2.125490607195605</v>
       </c>
     </row>
     <row r="78">
@@ -6282,7 +6282,7 @@
         <v>9.201412714429869</v>
       </c>
       <c r="V78" t="n">
-        <v>1.852881507831035</v>
+        <v>1.935188482474437</v>
       </c>
     </row>
     <row r="79">
@@ -6352,7 +6352,7 @@
         <v>0.5188709612521627</v>
       </c>
       <c r="V79" t="n">
-        <v>0.5292644544320984</v>
+        <v>0.5697391533935384</v>
       </c>
     </row>
     <row r="80">
@@ -6422,7 +6422,7 @@
         <v>0.04313317757317235</v>
       </c>
       <c r="V80" t="n">
-        <v>0.2883657218670598</v>
+        <v>0.3100563830787654</v>
       </c>
     </row>
     <row r="81">
@@ -6492,7 +6492,7 @@
         <v>4.219474442602377</v>
       </c>
       <c r="V81" t="n">
-        <v>0.7032354855860879</v>
+        <v>0.7523868825238689</v>
       </c>
     </row>
     <row r="82">
@@ -6562,7 +6562,7 @@
         <v>2.117897150761223</v>
       </c>
       <c r="V82" t="n">
-        <v>3.308746788434472</v>
+        <v>3.618918563090436</v>
       </c>
     </row>
     <row r="83">
@@ -6628,7 +6628,7 @@
         <v>0.613748691303573</v>
       </c>
       <c r="V83" t="n">
-        <v>2.743819960402773</v>
+        <v>2.525556835904057</v>
       </c>
     </row>
     <row r="84">
@@ -6696,7 +6696,7 @@
         <v>2.930160467059757</v>
       </c>
       <c r="V84" t="n">
-        <v>4.594360372718238</v>
+        <v>3.186443989997862</v>
       </c>
     </row>
     <row r="85">
@@ -6742,7 +6742,7 @@
         <v>7.416251594653059</v>
       </c>
       <c r="V85" t="n">
-        <v>15.54128078817734</v>
+        <v>13.18163672654691</v>
       </c>
     </row>
     <row r="86">
@@ -6806,7 +6806,7 @@
         <v>0.2338965517241379</v>
       </c>
       <c r="V86" t="n">
-        <v>1.597670477724662</v>
+        <v>1.705239509394124</v>
       </c>
     </row>
     <row r="87">
@@ -6862,7 +6862,7 @@
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>1.056686265969803</v>
+        <v>1.350379544546544</v>
       </c>
     </row>
     <row r="88">
@@ -6924,7 +6924,7 @@
         <v>0.5738739488801932</v>
       </c>
       <c r="V88" t="n">
-        <v>1.97242964390381</v>
+        <v>2.098377593476865</v>
       </c>
     </row>
     <row r="89">
@@ -6972,7 +6972,7 @@
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
       <c r="V89" t="n">
-        <v>0.5923259686181658</v>
+        <v>0.629808010592519</v>
       </c>
     </row>
     <row r="90">
@@ -7042,7 +7042,7 @@
         <v>5.570099683358743</v>
       </c>
       <c r="V90" t="n">
-        <v>0.6518347863479199</v>
+        <v>0.5979158332848142</v>
       </c>
     </row>
     <row r="91">
@@ -7108,7 +7108,7 @@
         <v>1.435611420960626</v>
       </c>
       <c r="V91" t="n">
-        <v>2.558756460059358</v>
+        <v>2.210381938648882</v>
       </c>
     </row>
     <row r="92">
@@ -7176,7 +7176,7 @@
         <v>3.591719426857714</v>
       </c>
       <c r="V92" t="n">
-        <v>0.9967218076830364</v>
+        <v>0.8497708216880939</v>
       </c>
     </row>
     <row r="93">
@@ -7246,7 +7246,7 @@
         <v>0.7742939029049041</v>
       </c>
       <c r="V93" t="n">
-        <v>0.7024851685454029</v>
+        <v>0.6966373687403318</v>
       </c>
     </row>
     <row r="94">
@@ -7310,7 +7310,7 @@
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="n">
-        <v>3.077257549320742</v>
+        <v>3.272172829961775</v>
       </c>
     </row>
     <row r="95">
@@ -7378,7 +7378,7 @@
         <v>0.423470083140248</v>
       </c>
       <c r="V95" t="n">
-        <v>1.521714889280548</v>
+        <v>1.509727389834116</v>
       </c>
     </row>
     <row r="96">
@@ -7442,7 +7442,7 @@
         <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>0.960146475434849</v>
+        <v>1.030194312201025</v>
       </c>
     </row>
     <row r="97">
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="V97" t="n">
-        <v>2.855767142133082</v>
+        <v>3.036417244401944</v>
       </c>
     </row>
     <row r="98">
@@ -7556,7 +7556,7 @@
         <v>0.85203125</v>
       </c>
       <c r="V98" t="n">
-        <v>0.70316327774066</v>
+        <v>0.7817282446291541</v>
       </c>
     </row>
     <row r="99">
@@ -7612,7 +7612,7 @@
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="n">
-        <v>3.238987146032667</v>
+        <v>3.241356202632629</v>
       </c>
     </row>
     <row r="100">
@@ -7682,7 +7682,7 @@
         <v>0.7458550821312432</v>
       </c>
       <c r="V100" t="n">
-        <v>1.645973635582229</v>
+        <v>1.708366368518007</v>
       </c>
     </row>
     <row r="101">
@@ -7752,7 +7752,7 @@
         <v>6.389186644517035</v>
       </c>
       <c r="V101" t="n">
-        <v>6.071894906981903</v>
+        <v>4.914686015009995</v>
       </c>
     </row>
     <row r="102">
@@ -7824,7 +7824,7 @@
         <v>5.779753417763986</v>
       </c>
       <c r="V102" t="n">
-        <v>6.417629019597408</v>
+        <v>5.022631078980819</v>
       </c>
     </row>
     <row r="103">
@@ -7950,7 +7950,7 @@
         <v>5.245948352626892</v>
       </c>
       <c r="V104" t="n">
-        <v>6.310654759325629</v>
+        <v>4.546684576251597</v>
       </c>
     </row>
   </sheetData>
@@ -8146,7 +8146,7 @@
         <v>0.07826810004799235</v>
       </c>
       <c r="V2" t="n">
-        <v>4.300967942658088e-07</v>
+        <v>1.154810055112495e-08</v>
       </c>
     </row>
     <row r="3">
@@ -8216,7 +8216,7 @@
         <v>0.00728378241221426</v>
       </c>
       <c r="V3" t="n">
-        <v>2.27048933285868e-197</v>
+        <v>8.772130469794586e-221</v>
       </c>
     </row>
     <row r="4">
@@ -8286,7 +8286,7 @@
         <v>1.446599781106859e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.354696876063484e-05</v>
+        <v>2.973032795482358e-08</v>
       </c>
     </row>
     <row r="5">
@@ -8356,7 +8356,7 @@
         <v>1.872107658682658e-183</v>
       </c>
       <c r="V5" t="n">
-        <v>1.804233202079323e-116</v>
+        <v>5.090706872650088e-84</v>
       </c>
     </row>
     <row r="6">
@@ -8426,7 +8426,7 @@
         <v>1.334455093903191e-15</v>
       </c>
       <c r="V6" t="n">
-        <v>3.338565811894694e-17</v>
+        <v>2.604566317955021e-10</v>
       </c>
     </row>
     <row r="7">
@@ -8496,7 +8496,7 @@
         <v>2.930505859766387e-16</v>
       </c>
       <c r="V7" t="n">
-        <v>5.231587980469752e-15</v>
+        <v>6.010435000971459e-10</v>
       </c>
     </row>
     <row r="8">
@@ -8636,7 +8636,7 @@
         <v>0.04845128137374613</v>
       </c>
       <c r="V9" t="n">
-        <v>5.377821880868281e-31</v>
+        <v>1.792786999005744e-23</v>
       </c>
     </row>
     <row r="10">
@@ -8706,7 +8706,7 @@
         <v>0.006900195795098495</v>
       </c>
       <c r="V10" t="n">
-        <v>9.556149803773801e-14</v>
+        <v>1.998650148062365e-10</v>
       </c>
     </row>
     <row r="11">
@@ -8846,7 +8846,7 @@
         <v>7.739767798405753e-177</v>
       </c>
       <c r="V12" t="n">
-        <v>9.881312916824931e-324</v>
+        <v>7.388314992698655e-295</v>
       </c>
     </row>
     <row r="13">
@@ -8916,7 +8916,7 @@
         <v>1.984948456397414e-10</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6551825013559475</v>
+        <v>0.01862255749114015</v>
       </c>
     </row>
     <row r="14">
@@ -8999,58 +8999,58 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>6.058000171136184e-70</v>
+        <v>5.769440164577318e-49</v>
       </c>
       <c r="D15" t="n">
-        <v>3.413899642410138e-40</v>
+        <v>6.111010213357524e-27</v>
       </c>
       <c r="E15" t="n">
-        <v>2.78751994193533e-49</v>
+        <v>7.66368647675057e-35</v>
       </c>
       <c r="F15" t="n">
-        <v>2.366581678505943e-51</v>
+        <v>2.060833769430591e-46</v>
       </c>
       <c r="G15" t="n">
-        <v>4.404192140029389e-158</v>
+        <v>2.353873001287612e-139</v>
       </c>
       <c r="H15" t="n">
-        <v>1.279057224585704e-08</v>
+        <v>8.20895849046389e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>4.583430311418615e-160</v>
+        <v>8.196625065980516e-151</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>9.696959018718441e-294</v>
       </c>
       <c r="K15" t="n">
-        <v>1.419883463196681e-28</v>
+        <v>4.463611105713972e-18</v>
       </c>
       <c r="L15" t="n">
-        <v>2.845631427674649e-27</v>
+        <v>6.565512220089234e-18</v>
       </c>
       <c r="M15" t="n">
-        <v>1.561620519344639e-245</v>
+        <v>1.626394886220089e-127</v>
       </c>
       <c r="N15" t="n">
-        <v>1.833847975058396e-88</v>
+        <v>2.703309049073346e-69</v>
       </c>
       <c r="O15" t="n">
-        <v>6.021242364457213e-246</v>
+        <v>2.633911406987127e-199</v>
       </c>
       <c r="P15" t="n">
-        <v>4.422885532711875e-47</v>
+        <v>3.02114313454475e-31</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.608533432882018e-39</v>
+        <v>3.581602732231459e-33</v>
       </c>
       <c r="R15" t="n">
-        <v>1.923904386187554e-27</v>
+        <v>9.992443006940072e-22</v>
       </c>
       <c r="S15" t="n">
-        <v>3.238075329899489e-24</v>
+        <v>4.711128369533865e-13</v>
       </c>
       <c r="T15" t="n">
-        <v>7.358251431834334e-121</v>
+        <v>2.010342601835422e-100</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -9196,7 +9196,7 @@
         <v>3.099456109315349e-25</v>
       </c>
       <c r="V17" t="n">
-        <v>6.719741000646594e-47</v>
+        <v>1.787820765256629e-50</v>
       </c>
     </row>
     <row r="18">
@@ -9266,7 +9266,7 @@
         <v>1.036308275423112e-107</v>
       </c>
       <c r="V18" t="n">
-        <v>2.163824027428805e-54</v>
+        <v>3.218809433620636e-50</v>
       </c>
     </row>
     <row r="19">
@@ -9406,7 +9406,7 @@
         <v>8.693502776822934e-145</v>
       </c>
       <c r="V20" t="n">
-        <v>1.103094725588907e-213</v>
+        <v>8.839595188201514e-216</v>
       </c>
     </row>
     <row r="21">
@@ -9476,7 +9476,7 @@
         <v>4.527045431499693e-06</v>
       </c>
       <c r="V21" t="n">
-        <v>4.309094384621663e-06</v>
+        <v>4.919199020746065e-05</v>
       </c>
     </row>
     <row r="22">
@@ -9546,7 +9546,7 @@
         <v>2.074006459486551e-08</v>
       </c>
       <c r="V22" t="n">
-        <v>1.068936332478506e-17</v>
+        <v>1.84621191196775e-15</v>
       </c>
     </row>
     <row r="23">
@@ -9616,7 +9616,7 @@
         <v>9.503726005255695e-62</v>
       </c>
       <c r="V23" t="n">
-        <v>2.373108201160219e-134</v>
+        <v>3.20140295920432e-127</v>
       </c>
     </row>
     <row r="24">
@@ -9686,7 +9686,7 @@
         <v>2.569765905239074e-31</v>
       </c>
       <c r="V24" t="n">
-        <v>1.531534733137452e-56</v>
+        <v>7.942915083288262e-54</v>
       </c>
     </row>
     <row r="25">
@@ -9756,7 +9756,7 @@
         <v>2.691655625056049e-74</v>
       </c>
       <c r="V25" t="n">
-        <v>4.90923240808915e-143</v>
+        <v>5.926753579347088e-139</v>
       </c>
     </row>
     <row r="26">
@@ -9826,7 +9826,7 @@
         <v>0.0004470824807386081</v>
       </c>
       <c r="V26" t="n">
-        <v>2.367617448622769e-10</v>
+        <v>6.411452362836273e-07</v>
       </c>
     </row>
     <row r="27">
@@ -9896,7 +9896,7 @@
         <v>0.0660670682811022</v>
       </c>
       <c r="V27" t="n">
-        <v>0.5697844372562564</v>
+        <v>0.5559816984703441</v>
       </c>
     </row>
     <row r="28">
@@ -9966,7 +9966,7 @@
         <v>1.757315674317565e-40</v>
       </c>
       <c r="V28" t="n">
-        <v>1.156821202404e-64</v>
+        <v>9.922291698350225e-60</v>
       </c>
     </row>
     <row r="29">
@@ -10036,7 +10036,7 @@
         <v>8.199734062322229e-13</v>
       </c>
       <c r="V29" t="n">
-        <v>9.564342907761686e-31</v>
+        <v>3.60938327379544e-26</v>
       </c>
     </row>
     <row r="30">
@@ -10106,7 +10106,7 @@
         <v>2.309727828491841e-11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.175178358249205e-18</v>
+        <v>2.204700895156089e-17</v>
       </c>
     </row>
     <row r="31">
@@ -10176,7 +10176,7 @@
         <v>6.18548927794206e-19</v>
       </c>
       <c r="V31" t="n">
-        <v>7.447108117167911e-56</v>
+        <v>8.907913975484098e-54</v>
       </c>
     </row>
     <row r="32">
@@ -10246,7 +10246,7 @@
         <v>2.349987878827249e-21</v>
       </c>
       <c r="V32" t="n">
-        <v>3.397460056031111e-87</v>
+        <v>2.190523035630461e-83</v>
       </c>
     </row>
     <row r="33">
@@ -10316,7 +10316,7 @@
         <v>6.089379345892176e-15</v>
       </c>
       <c r="V33" t="n">
-        <v>3.389915490574779e-09</v>
+        <v>9.166564201100911e-07</v>
       </c>
     </row>
     <row r="34">
@@ -10386,7 +10386,7 @@
         <v>1.452715523405959e-19</v>
       </c>
       <c r="V34" t="n">
-        <v>2.762208124084267e-80</v>
+        <v>7.832120410790039e-77</v>
       </c>
     </row>
     <row r="35">
@@ -10456,7 +10456,7 @@
         <v>8.169331559846961e-08</v>
       </c>
       <c r="V35" t="n">
-        <v>0.2881940243979667</v>
+        <v>0.2149479858316783</v>
       </c>
     </row>
     <row r="36">
@@ -10526,7 +10526,7 @@
         <v>0.749209472132881</v>
       </c>
       <c r="V36" t="n">
-        <v>9.163987365793828e-05</v>
+        <v>0.0001661163767468764</v>
       </c>
     </row>
     <row r="37">
@@ -10596,7 +10596,7 @@
         <v>3.349907260557344e-06</v>
       </c>
       <c r="V37" t="n">
-        <v>0.02423558746041866</v>
+        <v>0.03867057455998079</v>
       </c>
     </row>
     <row r="38">
@@ -10666,7 +10666,7 @@
         <v>4.489045081204884e-09</v>
       </c>
       <c r="V38" t="n">
-        <v>1.911163160709961e-20</v>
+        <v>1.771233880999017e-19</v>
       </c>
     </row>
     <row r="39">
@@ -10736,7 +10736,7 @@
         <v>1.438567517666629e-13</v>
       </c>
       <c r="V39" t="n">
-        <v>1.470990227703387e-06</v>
+        <v>1.325951199484752e-05</v>
       </c>
     </row>
     <row r="40">
@@ -10806,7 +10806,7 @@
         <v>4.23800174149861e-33</v>
       </c>
       <c r="V40" t="n">
-        <v>6.234342361264328e-67</v>
+        <v>4.450619917610017e-57</v>
       </c>
     </row>
     <row r="41">
@@ -10876,7 +10876,7 @@
         <v>3.934239671353527e-73</v>
       </c>
       <c r="V41" t="n">
-        <v>9.114388156279905e-105</v>
+        <v>4.111901093298523e-94</v>
       </c>
     </row>
     <row r="42">
@@ -10946,7 +10946,7 @@
         <v>0.459265930584968</v>
       </c>
       <c r="V42" t="n">
-        <v>0.002278017142822699</v>
+        <v>0.009432564635446143</v>
       </c>
     </row>
     <row r="43">
@@ -11016,7 +11016,7 @@
         <v>0.9090609308626145</v>
       </c>
       <c r="V43" t="n">
-        <v>5.794665311703111e-12</v>
+        <v>5.477986360801346e-12</v>
       </c>
     </row>
     <row r="44">
@@ -11086,7 +11086,7 @@
         <v>6.170470483480249e-16</v>
       </c>
       <c r="V44" t="n">
-        <v>1.801104142572209e-16</v>
+        <v>5.001330161300118e-14</v>
       </c>
     </row>
     <row r="45">
@@ -11156,7 +11156,7 @@
         <v>4.378932919294283e-11</v>
       </c>
       <c r="V45" t="n">
-        <v>2.485426105753696e-27</v>
+        <v>6.868600119100331e-26</v>
       </c>
     </row>
     <row r="46">
@@ -11226,7 +11226,7 @@
         <v>0.006811109215633314</v>
       </c>
       <c r="V46" t="n">
-        <v>5.084430559992823e-05</v>
+        <v>7.275111502075318e-05</v>
       </c>
     </row>
     <row r="47">
@@ -11296,7 +11296,7 @@
         <v>0.3874515454754064</v>
       </c>
       <c r="V47" t="n">
-        <v>0.3538668974958186</v>
+        <v>0.5932840191370655</v>
       </c>
     </row>
     <row r="48">
@@ -11366,7 +11366,7 @@
         <v>0.004253523308637492</v>
       </c>
       <c r="V48" t="n">
-        <v>2.624544637394214e-12</v>
+        <v>7.28390696728633e-12</v>
       </c>
     </row>
     <row r="49">
@@ -11436,7 +11436,7 @@
         <v>8.616722658659301e-05</v>
       </c>
       <c r="V49" t="n">
-        <v>5.413692977922531e-09</v>
+        <v>1.944698050318417e-07</v>
       </c>
     </row>
     <row r="50">
@@ -11506,7 +11506,7 @@
         <v>0.09071461374198493</v>
       </c>
       <c r="V50" t="n">
-        <v>0.4890541525763022</v>
+        <v>0.308086673324667</v>
       </c>
     </row>
     <row r="51">
@@ -11576,7 +11576,7 @@
         <v>6.224485647796934e-18</v>
       </c>
       <c r="V51" t="n">
-        <v>1.119076749445393e-155</v>
+        <v>1.610326354097893e-156</v>
       </c>
     </row>
     <row r="52">
@@ -11646,7 +11646,7 @@
         <v>5.660411094112265e-08</v>
       </c>
       <c r="V52" t="n">
-        <v>9.134763576021557e-05</v>
+        <v>8.144542150541697e-05</v>
       </c>
     </row>
     <row r="53">
@@ -11716,7 +11716,7 @@
         <v>2.170389827576657e-20</v>
       </c>
       <c r="V53" t="n">
-        <v>5.011978974823691e-61</v>
+        <v>1.514843163651236e-59</v>
       </c>
     </row>
     <row r="54">
@@ -11786,7 +11786,7 @@
         <v>1.470094544931561e-24</v>
       </c>
       <c r="V54" t="n">
-        <v>1.272178060894783e-35</v>
+        <v>1.089721566901796e-34</v>
       </c>
     </row>
     <row r="55">
@@ -11856,7 +11856,7 @@
         <v>2.324581164210319e-12</v>
       </c>
       <c r="V55" t="n">
-        <v>1.051415641503826e-79</v>
+        <v>4.191120016203026e-80</v>
       </c>
     </row>
     <row r="56">
@@ -11926,7 +11926,7 @@
         <v>1.90918764542513e-07</v>
       </c>
       <c r="V56" t="n">
-        <v>7.66873956964697e-09</v>
+        <v>1.928871694767925e-09</v>
       </c>
     </row>
     <row r="57">
@@ -11996,7 +11996,7 @@
         <v>7.781476083575562e-68</v>
       </c>
       <c r="V57" t="n">
-        <v>8.751622391369913e-150</v>
+        <v>1.030810186787287e-132</v>
       </c>
     </row>
     <row r="58">
@@ -12066,7 +12066,7 @@
         <v>0.006340928901980973</v>
       </c>
       <c r="V58" t="n">
-        <v>9.171596630797012e-77</v>
+        <v>8.662072409453282e-75</v>
       </c>
     </row>
     <row r="59">
@@ -12136,7 +12136,7 @@
         <v>1.809650611471714e-64</v>
       </c>
       <c r="V59" t="n">
-        <v>1.510628174444129e-66</v>
+        <v>1.938527490286694e-56</v>
       </c>
     </row>
     <row r="60">
@@ -12206,7 +12206,7 @@
         <v>9.260777705735819e-06</v>
       </c>
       <c r="V60" t="n">
-        <v>0.0006551284515414989</v>
+        <v>0.006944392067121346</v>
       </c>
     </row>
     <row r="61">
@@ -12276,7 +12276,7 @@
         <v>7.55816654526151e-29</v>
       </c>
       <c r="V61" t="n">
-        <v>4.787786751500142e-129</v>
+        <v>6.870373244180875e-131</v>
       </c>
     </row>
     <row r="62">
@@ -12416,7 +12416,7 @@
         <v>0.3270750250392694</v>
       </c>
       <c r="V63" t="n">
-        <v>5.722314856471953e-13</v>
+        <v>1.547119410695481e-12</v>
       </c>
     </row>
     <row r="64">
@@ -12486,7 +12486,7 @@
         <v>5.735729022605185e-145</v>
       </c>
       <c r="V64" t="n">
-        <v>9.316116528075112e-253</v>
+        <v>4.673135223147289e-238</v>
       </c>
     </row>
     <row r="65">
@@ -12556,7 +12556,7 @@
         <v>1.89114636457552e-60</v>
       </c>
       <c r="V65" t="n">
-        <v>3.643486230871244e-311</v>
+        <v>4.27601372593764e-304</v>
       </c>
     </row>
     <row r="66">
@@ -12696,7 +12696,7 @@
         <v>5.652724869875359e-46</v>
       </c>
       <c r="V67" t="n">
-        <v>1.037997347796593e-34</v>
+        <v>9.513271894318013e-33</v>
       </c>
     </row>
     <row r="68">
@@ -12766,7 +12766,7 @@
         <v>2.936895979950122e-20</v>
       </c>
       <c r="V68" t="n">
-        <v>2.534233136849422e-301</v>
+        <v>1.232153093742531e-298</v>
       </c>
     </row>
     <row r="69">
@@ -12906,7 +12906,7 @@
         <v>0.04422824888347477</v>
       </c>
       <c r="V70" t="n">
-        <v>3.009158843757811e-19</v>
+        <v>3.88414134314091e-18</v>
       </c>
     </row>
     <row r="71">
@@ -12976,7 +12976,7 @@
         <v>8.661271297808827e-25</v>
       </c>
       <c r="V71" t="n">
-        <v>3.570317474436293e-135</v>
+        <v>3.987939522419224e-106</v>
       </c>
     </row>
     <row r="72">
@@ -13046,7 +13046,7 @@
         <v>0.1160699115355252</v>
       </c>
       <c r="V72" t="n">
-        <v>0.0001048799094006012</v>
+        <v>6.092329034568495e-05</v>
       </c>
     </row>
     <row r="73">
@@ -13116,7 +13116,7 @@
         <v>1</v>
       </c>
       <c r="V73" t="n">
-        <v>2.530292187240758e-07</v>
+        <v>6.343470606486427e-08</v>
       </c>
     </row>
     <row r="74">
@@ -13186,7 +13186,7 @@
         <v>0.1745660640432095</v>
       </c>
       <c r="V74" t="n">
-        <v>1.268723278579322e-65</v>
+        <v>2.879464345608012e-69</v>
       </c>
     </row>
     <row r="75">
@@ -13326,7 +13326,7 @@
         <v>2.698127956273127e-43</v>
       </c>
       <c r="V76" t="n">
-        <v>1.0475887404235e-20</v>
+        <v>1.119015965684244e-13</v>
       </c>
     </row>
     <row r="77">
@@ -13396,7 +13396,7 @@
         <v>1.49854541587716e-08</v>
       </c>
       <c r="V77" t="n">
-        <v>9.090693341013316e-101</v>
+        <v>2.293086653139771e-122</v>
       </c>
     </row>
     <row r="78">
@@ -13466,7 +13466,7 @@
         <v>1.213845231848771e-19</v>
       </c>
       <c r="V78" t="n">
-        <v>0.001457348436569215</v>
+        <v>0.001129529839914554</v>
       </c>
     </row>
     <row r="79">
@@ -13536,7 +13536,7 @@
         <v>0.02177208852473654</v>
       </c>
       <c r="V79" t="n">
-        <v>5.71687612427004e-23</v>
+        <v>1.108536265530666e-17</v>
       </c>
     </row>
     <row r="80">
@@ -13606,7 +13606,7 @@
         <v>7.295357844824349e-133</v>
       </c>
       <c r="V80" t="n">
-        <v>3.551660847623993e-174</v>
+        <v>1.549310447457322e-149</v>
       </c>
     </row>
     <row r="81">
@@ -13676,7 +13676,7 @@
         <v>2.297303469310728e-234</v>
       </c>
       <c r="V81" t="n">
-        <v>1.149786350502456e-17</v>
+        <v>1.201057141604554e-11</v>
       </c>
     </row>
     <row r="82">
@@ -13816,7 +13816,7 @@
         <v>2.571673894939216e-64</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>2.059846178255277e-267</v>
       </c>
     </row>
     <row r="84">
@@ -13886,7 +13886,7 @@
         <v>1.382460136669044e-219</v>
       </c>
       <c r="V84" t="n">
-        <v>1.138756288859804e-171</v>
+        <v>2.007342740541051e-72</v>
       </c>
     </row>
     <row r="85">
@@ -13956,7 +13956,7 @@
         <v>9.421522462014081e-73</v>
       </c>
       <c r="V85" t="n">
-        <v>3.065763973822784e-16</v>
+        <v>3.059259793031223e-11</v>
       </c>
     </row>
     <row r="86">
@@ -14026,7 +14026,7 @@
         <v>3.542248480542179e-09</v>
       </c>
       <c r="V86" t="n">
-        <v>6.188466568228982e-06</v>
+        <v>5.109306667471977e-07</v>
       </c>
     </row>
     <row r="87">
@@ -14096,7 +14096,7 @@
         <v>1.08323753178313e-08</v>
       </c>
       <c r="V87" t="n">
-        <v>0.7700391095198582</v>
+        <v>0.1341688650837803</v>
       </c>
     </row>
     <row r="88">
@@ -14166,7 +14166,7 @@
         <v>0.2428607623805569</v>
       </c>
       <c r="V88" t="n">
-        <v>8.659109713703354e-07</v>
+        <v>7.356062023811162e-08</v>
       </c>
     </row>
     <row r="89">
@@ -14236,7 +14236,7 @@
         <v>1</v>
       </c>
       <c r="V89" t="n">
-        <v>0.1179851971998795</v>
+        <v>0.1921067790189407</v>
       </c>
     </row>
     <row r="90">
@@ -14306,7 +14306,7 @@
         <v>4.60068667044018e-18</v>
       </c>
       <c r="V90" t="n">
-        <v>2.278370594097847e-10</v>
+        <v>1.502244756621069e-13</v>
       </c>
     </row>
     <row r="91">
@@ -14376,7 +14376,7 @@
         <v>0.7431320300768266</v>
       </c>
       <c r="V91" t="n">
-        <v>0.0001188567131996298</v>
+        <v>0.005022456813891987</v>
       </c>
     </row>
     <row r="92">
@@ -14446,7 +14446,7 @@
         <v>0.03209999216276199</v>
       </c>
       <c r="V92" t="n">
-        <v>1</v>
+        <v>0.475064139955826</v>
       </c>
     </row>
     <row r="93">
@@ -14516,7 +14516,7 @@
         <v>0.07443386053595223</v>
       </c>
       <c r="V93" t="n">
-        <v>5.308672346717493e-06</v>
+        <v>1.025233143810137e-05</v>
       </c>
     </row>
     <row r="94">
@@ -14586,7 +14586,7 @@
         <v>1</v>
       </c>
       <c r="V94" t="n">
-        <v>0.003839347493540187</v>
+        <v>0.002687887958459319</v>
       </c>
     </row>
     <row r="95">
@@ -14656,7 +14656,7 @@
         <v>0.01530826189088328</v>
       </c>
       <c r="V95" t="n">
-        <v>0.003950101348170641</v>
+        <v>0.007271155083226933</v>
       </c>
     </row>
     <row r="96">
@@ -14726,7 +14726,7 @@
         <v>0.005315297832767727</v>
       </c>
       <c r="V96" t="n">
-        <v>0.925927588510951</v>
+        <v>0.8501986263944209</v>
       </c>
     </row>
     <row r="97">
@@ -14796,7 +14796,7 @@
         <v>1</v>
       </c>
       <c r="V97" t="n">
-        <v>0.2776214698687453</v>
+        <v>0.2579475502345484</v>
       </c>
     </row>
     <row r="98">
@@ -14866,7 +14866,7 @@
         <v>0.732114865225017</v>
       </c>
       <c r="V98" t="n">
-        <v>0.218752881359108</v>
+        <v>0.4450443657655037</v>
       </c>
     </row>
     <row r="99">
@@ -14936,7 +14936,7 @@
         <v>1</v>
       </c>
       <c r="V99" t="n">
-        <v>0.001009378080210811</v>
+        <v>0.001316024522988446</v>
       </c>
     </row>
     <row r="100">
@@ -15006,7 +15006,7 @@
         <v>0.320941723510821</v>
       </c>
       <c r="V100" t="n">
-        <v>0.0001714890009112365</v>
+        <v>8.013832555752214e-05</v>
       </c>
     </row>
     <row r="101">
@@ -15076,7 +15076,7 @@
         <v>2.579369639147731e-54</v>
       </c>
       <c r="V101" t="n">
-        <v>1.513287113148421e-117</v>
+        <v>1.226267612821395e-71</v>
       </c>
     </row>
     <row r="102">
@@ -15146,7 +15146,7 @@
         <v>4.55512206037536e-12</v>
       </c>
       <c r="V102" t="n">
-        <v>1.462364543002175e-39</v>
+        <v>4.922847912870398e-23</v>
       </c>
     </row>
     <row r="103">
@@ -15216,7 +15216,7 @@
         <v>0.5134818495686181</v>
       </c>
       <c r="V103" t="n">
-        <v>5.301963001467656e-06</v>
+        <v>3.510851452555388e-06</v>
       </c>
     </row>
     <row r="104">
@@ -15286,7 +15286,7 @@
         <v>8.406250005400932e-85</v>
       </c>
       <c r="V104" t="n">
-        <v>6.51941951678524e-160</v>
+        <v>2.290017549918152e-80</v>
       </c>
     </row>
   </sheetData>
@@ -15440,7 +15440,7 @@
         <v>0.3427896363117255</v>
       </c>
       <c r="H2" t="n">
-        <v>2.977818461569568e-05</v>
+        <v>3.134545749020598e-05</v>
       </c>
       <c r="I2" t="n">
         <v>0.1391323710242499</v>
@@ -15482,7 +15482,7 @@
         <v>0.09484252123462603</v>
       </c>
       <c r="V2" t="n">
-        <v>6.152773584635877e-07</v>
+        <v>1.749197583479221e-08</v>
       </c>
     </row>
     <row r="3">
@@ -15498,7 +15498,7 @@
         <v>4.076971179787449e-18</v>
       </c>
       <c r="D3" t="n">
-        <v>7.788213382646871e-27</v>
+        <v>8.30742760815666e-27</v>
       </c>
       <c r="E3" t="n">
         <v>0.1039817400047706</v>
@@ -15519,7 +15519,7 @@
         <v>3.356936347320967e-79</v>
       </c>
       <c r="K3" t="n">
-        <v>1.767626756877745e-26</v>
+        <v>1.903598045868341e-26</v>
       </c>
       <c r="L3" t="n">
         <v>0.0001549334648319704</v>
@@ -15552,7 +15552,7 @@
         <v>0.009743241408546348</v>
       </c>
       <c r="V3" t="n">
-        <v>1.299224451580245e-196</v>
+        <v>5.314879049346131e-220</v>
       </c>
     </row>
     <row r="4">
@@ -15622,7 +15622,7 @@
         <v>2.442619302524696e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.766250357399226e-05</v>
+        <v>4.438005477314244e-08</v>
       </c>
     </row>
     <row r="5">
@@ -15692,7 +15692,7 @@
         <v>1.483285298802414e-182</v>
       </c>
       <c r="V5" t="n">
-        <v>6.408138614281732e-116</v>
+        <v>1.872652885296282e-83</v>
       </c>
     </row>
     <row r="6">
@@ -15762,7 +15762,7 @@
         <v>2.80507907493936e-15</v>
       </c>
       <c r="V6" t="n">
-        <v>5.928832390088854e-17</v>
+        <v>4.127235857682572e-10</v>
       </c>
     </row>
     <row r="7">
@@ -15832,7 +15832,7 @@
         <v>6.422172416083783e-16</v>
       </c>
       <c r="V7" t="n">
-        <v>8.833664950629254e-15</v>
+        <v>9.379921289394851e-10</v>
       </c>
     </row>
     <row r="8">
@@ -15845,7 +15845,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>8.318463142119411e-55</v>
+        <v>9.358271034884337e-55</v>
       </c>
       <c r="D8" t="n">
         <v>4.375586350635936e-67</v>
@@ -15872,19 +15872,19 @@
         <v>1.513477320735167e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.88845008424914e-20</v>
+        <v>4.320500093610156e-20</v>
       </c>
       <c r="M8" t="n">
         <v>8.158550329073735e-24</v>
       </c>
       <c r="N8" t="n">
-        <v>7.610604571209495e-71</v>
+        <v>8.371665028330444e-71</v>
       </c>
       <c r="O8" t="n">
         <v>1.750602403168702e-186</v>
       </c>
       <c r="P8" t="n">
-        <v>2.21796745673042e-44</v>
+        <v>2.495213388821723e-44</v>
       </c>
       <c r="Q8" t="n">
         <v>1.257791604691092e-38</v>
@@ -15972,7 +15972,7 @@
         <v>0.06085953635970551</v>
       </c>
       <c r="V9" t="n">
-        <v>1.153990945269652e-30</v>
+        <v>3.768511446889625e-23</v>
       </c>
     </row>
     <row r="10">
@@ -16042,7 +16042,7 @@
         <v>0.009351581143357173</v>
       </c>
       <c r="V10" t="n">
-        <v>1.587553919014035e-13</v>
+        <v>3.216577582037869e-10</v>
       </c>
     </row>
     <row r="11">
@@ -16100,7 +16100,7 @@
         <v>3.28198875233595e-46</v>
       </c>
       <c r="R11" t="n">
-        <v>3.900145225221695e-25</v>
+        <v>4.290159747743864e-25</v>
       </c>
       <c r="S11" t="n">
         <v>9.572452779033843e-33</v>
@@ -16128,7 +16128,7 @@
         <v>4.041917857520019e-32</v>
       </c>
       <c r="D12" t="n">
-        <v>6.237817486410365e-34</v>
+        <v>6.717649600749625e-34</v>
       </c>
       <c r="E12" t="n">
         <v>4.138175752329971e-28</v>
@@ -16140,19 +16140,19 @@
         <v>7.044657396722454e-55</v>
       </c>
       <c r="H12" t="n">
-        <v>6.764916610033225e-05</v>
+        <v>7.046788135451276e-05</v>
       </c>
       <c r="I12" t="n">
         <v>1.103642615848686e-09</v>
       </c>
       <c r="J12" t="n">
-        <v>1.306986778401581e-308</v>
+        <v>1.42580375825627e-308</v>
       </c>
       <c r="K12" t="n">
         <v>1.235110023102368e-16</v>
       </c>
       <c r="L12" t="n">
-        <v>1.09552836064285e-21</v>
+        <v>1.252032412163257e-21</v>
       </c>
       <c r="M12" t="n">
         <v>5.012810698065982e-55</v>
@@ -16182,7 +16182,7 @@
         <v>5.694257737398518e-176</v>
       </c>
       <c r="V12" t="n">
-        <v>7.905050333459945e-323</v>
+        <v>5.435688887485439e-294</v>
       </c>
     </row>
     <row r="13">
@@ -16210,7 +16210,7 @@
         <v>0.002881590985993019</v>
       </c>
       <c r="H13" t="n">
-        <v>3.046132908033604e-05</v>
+        <v>3.184593494762403e-05</v>
       </c>
       <c r="I13" t="n">
         <v>2.389463683146445e-18</v>
@@ -16225,7 +16225,7 @@
         <v>0.1024132000120364</v>
       </c>
       <c r="M13" t="n">
-        <v>3.157350100506327e-142</v>
+        <v>3.47308511055696e-142</v>
       </c>
       <c r="N13" t="n">
         <v>0.0008174524377210552</v>
@@ -16252,7 +16252,7 @@
         <v>3.586836684367257e-10</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6748379763966259</v>
+        <v>0.02084916762595039</v>
       </c>
     </row>
     <row r="14">
@@ -16286,10 +16286,10 @@
         <v>3.909235778767218e-214</v>
       </c>
       <c r="J14" t="n">
-        <v>7.550652599107206e-317</v>
+        <v>8.305717809611362e-317</v>
       </c>
       <c r="K14" t="n">
-        <v>1.408410319147348e-20</v>
+        <v>1.502304340423838e-20</v>
       </c>
       <c r="L14" t="n">
         <v>6.611491888792683e-30</v>
@@ -16307,7 +16307,7 @@
         <v>7.501702069528412e-49</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.94229734634624e-36</v>
+        <v>4.336527080980864e-36</v>
       </c>
       <c r="R14" t="n">
         <v>4.292221712839206e-20</v>
@@ -16335,58 +16335,58 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>8.913914537528955e-69</v>
+        <v>6.602803743905154e-48</v>
       </c>
       <c r="D15" t="n">
-        <v>2.704858947448032e-39</v>
+        <v>3.702553246916617e-26</v>
       </c>
       <c r="E15" t="n">
-        <v>2.392621283494491e-48</v>
+        <v>4.933498169408179e-34</v>
       </c>
       <c r="F15" t="n">
-        <v>1.741127949186515e-50</v>
+        <v>1.516184844652506e-45</v>
       </c>
       <c r="G15" t="n">
-        <v>5.040353226922523e-157</v>
+        <v>2.693876879251378e-138</v>
       </c>
       <c r="H15" t="n">
-        <v>8.782859608821831e-08</v>
+        <v>0.0002818409081725935</v>
       </c>
       <c r="I15" t="n">
-        <v>3.934111017300978e-159</v>
+        <v>7.03543651496661e-150</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>8.323223157733329e-293</v>
       </c>
       <c r="K15" t="n">
-        <v>1.124984590071216e-27</v>
+        <v>2.554177466047439e-17</v>
       </c>
       <c r="L15" t="n">
-        <v>4.187143386435554e-26</v>
+        <v>5.201905835916855e-17</v>
       </c>
       <c r="M15" t="n">
-        <v>2.010586418656223e-244</v>
+        <v>1.288605179082071e-126</v>
       </c>
       <c r="N15" t="n">
-        <v>2.361079267887685e-87</v>
+        <v>2.320340267121289e-68</v>
       </c>
       <c r="O15" t="n">
-        <v>6.890977372656588e-245</v>
+        <v>3.014365276885268e-198</v>
       </c>
       <c r="P15" t="n">
-        <v>5.694465123366539e-46</v>
+        <v>3.111777428581093e-30</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.746789435868479e-38</v>
+        <v>3.353682558362184e-32</v>
       </c>
       <c r="R15" t="n">
-        <v>2.201801686414645e-26</v>
+        <v>7.917089459344826e-21</v>
       </c>
       <c r="S15" t="n">
-        <v>5.558695982994124e-23</v>
+        <v>5.391624689577646e-12</v>
       </c>
       <c r="T15" t="n">
-        <v>6.88999906799033e-120</v>
+        <v>1.725544066575404e-99</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -16420,7 +16420,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.327061582075423e-05</v>
+        <v>1.400787225524057e-05</v>
       </c>
       <c r="I16" t="n">
         <v>2.114893942504447e-95</v>
@@ -16532,7 +16532,7 @@
         <v>8.867888312763361e-25</v>
       </c>
       <c r="V17" t="n">
-        <v>1.573030279696816e-46</v>
+        <v>4.282454391196111e-50</v>
       </c>
     </row>
     <row r="18">
@@ -16602,7 +16602,7 @@
         <v>5.92998624269892e-107</v>
       </c>
       <c r="V18" t="n">
-        <v>5.183113368027138e-54</v>
+        <v>7.534940265066489e-50</v>
       </c>
     </row>
     <row r="19">
@@ -16663,7 +16663,7 @@
         <v>6.110985712301674e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>5.968620366167781e-14</v>
+        <v>6.714697911938754e-14</v>
       </c>
       <c r="T19" t="n">
         <v>3.888884682954186e-148</v>
@@ -16691,7 +16691,7 @@
         <v>2.645690819564202e-17</v>
       </c>
       <c r="E20" t="n">
-        <v>5.075424154105194e-45</v>
+        <v>5.498376166947294e-45</v>
       </c>
       <c r="F20" t="n">
         <v>1.718918921005798e-27</v>
@@ -16709,13 +16709,13 @@
         <v>6.710399760140696e-49</v>
       </c>
       <c r="K20" t="n">
-        <v>6.972048374202521e-23</v>
+        <v>7.470051829502702e-23</v>
       </c>
       <c r="L20" t="n">
         <v>1.801625616517422e-13</v>
       </c>
       <c r="M20" t="n">
-        <v>1.88325659508248e-162</v>
+        <v>2.11866366946779e-162</v>
       </c>
       <c r="N20" t="n">
         <v>1.550022949155754e-52</v>
@@ -16736,13 +16736,13 @@
         <v>5.057452038320185e-11</v>
       </c>
       <c r="T20" t="n">
-        <v>9.723307752646645e-118</v>
+        <v>1.060724482106907e-117</v>
       </c>
       <c r="U20" t="n">
         <v>5.596442412579764e-144</v>
       </c>
       <c r="V20" t="n">
-        <v>6.683456278568082e-213</v>
+        <v>5.058212802137533e-215</v>
       </c>
     </row>
     <row r="21">
@@ -16812,7 +16812,7 @@
         <v>6.857142344771593e-06</v>
       </c>
       <c r="V21" t="n">
-        <v>5.917822954880417e-06</v>
+        <v>6.413639229580314e-05</v>
       </c>
     </row>
     <row r="22">
@@ -16882,7 +16882,7 @@
         <v>3.39083595757325e-08</v>
       </c>
       <c r="V22" t="n">
-        <v>1.966079325808681e-17</v>
+        <v>3.457451398775968e-15</v>
       </c>
     </row>
     <row r="23">
@@ -16910,7 +16910,7 @@
         <v>1.342189374297886e-32</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0001438529389682338</v>
+        <v>0.0001493857443131659</v>
       </c>
       <c r="I23" t="n">
         <v>0.0273289691177373</v>
@@ -16952,7 +16952,7 @@
         <v>3.764937609774372e-61</v>
       </c>
       <c r="V23" t="n">
-        <v>9.401159412288559e-134</v>
+        <v>1.373935436658521e-126</v>
       </c>
     </row>
     <row r="24">
@@ -17022,7 +17022,7 @@
         <v>7.784879065871311e-31</v>
       </c>
       <c r="V24" t="n">
-        <v>3.84751408568677e-56</v>
+        <v>1.995415252630954e-53</v>
       </c>
     </row>
     <row r="25">
@@ -17092,7 +17092,7 @@
         <v>1.386202646903865e-73</v>
       </c>
       <c r="V25" t="n">
-        <v>2.106878908471594e-142</v>
+        <v>2.906931517489286e-138</v>
       </c>
     </row>
     <row r="26">
@@ -17162,7 +17162,7 @@
         <v>0.0006485844438884034</v>
       </c>
       <c r="V26" t="n">
-        <v>3.639770107584258e-10</v>
+        <v>8.92404855908292e-07</v>
       </c>
     </row>
     <row r="27">
@@ -17232,7 +17232,7 @@
         <v>0.08198684377052443</v>
       </c>
       <c r="V27" t="n">
-        <v>0.5928060306807517</v>
+        <v>0.5669912370539153</v>
       </c>
     </row>
     <row r="28">
@@ -17302,7 +17302,7 @@
         <v>5.656359826709662e-40</v>
       </c>
       <c r="V28" t="n">
-        <v>3.055194457631078e-64</v>
+        <v>2.762151472783982e-59</v>
       </c>
     </row>
     <row r="29">
@@ -17372,7 +17372,7 @@
         <v>1.624178093113826e-12</v>
       </c>
       <c r="V29" t="n">
-        <v>2.010463917345824e-30</v>
+        <v>7.909925046828304e-26</v>
       </c>
     </row>
     <row r="30">
@@ -17442,7 +17442,7 @@
         <v>4.325490296993811e-11</v>
       </c>
       <c r="V30" t="n">
-        <v>2.200788561812147e-18</v>
+        <v>4.205262818538467e-17</v>
       </c>
     </row>
     <row r="31">
@@ -17470,7 +17470,7 @@
         <v>0.0001830234682211585</v>
       </c>
       <c r="H31" t="n">
-        <v>2.507072769544436e-07</v>
+        <v>2.663764817640964e-07</v>
       </c>
       <c r="I31" t="n">
         <v>1.193984711687821e-06</v>
@@ -17512,7 +17512,7 @@
         <v>1.447966808245528e-18</v>
       </c>
       <c r="V31" t="n">
-        <v>1.826314609686416e-55</v>
+        <v>2.184559855892529e-53</v>
       </c>
     </row>
     <row r="32">
@@ -17582,7 +17582,7 @@
         <v>6.206378244082222e-21</v>
       </c>
       <c r="V32" t="n">
-        <v>1.093557455535014e-86</v>
+        <v>7.780133540342673e-83</v>
       </c>
     </row>
     <row r="33">
@@ -17652,7 +17652,7 @@
         <v>1.254412145253788e-14</v>
       </c>
       <c r="V33" t="n">
-        <v>5.134724934252974e-09</v>
+        <v>1.258874816951192e-06</v>
       </c>
     </row>
     <row r="34">
@@ -17722,7 +17722,7 @@
         <v>3.479760439786366e-19</v>
       </c>
       <c r="V34" t="n">
-        <v>8.62143747820241e-80</v>
+        <v>2.520963757223044e-76</v>
       </c>
     </row>
     <row r="35">
@@ -17792,7 +17792,7 @@
         <v>1.294524847175749e-07</v>
       </c>
       <c r="V35" t="n">
-        <v>0.3092081720103185</v>
+        <v>0.2306212764652382</v>
       </c>
     </row>
     <row r="36">
@@ -17862,7 +17862,7 @@
         <v>0.7955523260792448</v>
       </c>
       <c r="V36" t="n">
-        <v>0.0001151086217898493</v>
+        <v>0.0002036903191062889</v>
       </c>
     </row>
     <row r="37">
@@ -17932,7 +17932,7 @@
         <v>5.149857430409051e-06</v>
       </c>
       <c r="V37" t="n">
-        <v>0.02713332074372959</v>
+        <v>0.04282870085675292</v>
       </c>
     </row>
     <row r="38">
@@ -18002,7 +18002,7 @@
         <v>7.836807514645814e-09</v>
       </c>
       <c r="V38" t="n">
-        <v>3.714147274587282e-20</v>
+        <v>3.577197838096054e-19</v>
       </c>
     </row>
     <row r="39">
@@ -18072,7 +18072,7 @@
         <v>2.905342241562015e-13</v>
       </c>
       <c r="V39" t="n">
-        <v>2.047459370992553e-06</v>
+        <v>1.750935558293968e-05</v>
       </c>
     </row>
     <row r="40">
@@ -18142,7 +18142,7 @@
         <v>1.322770240528354e-32</v>
       </c>
       <c r="V40" t="n">
-        <v>1.783714620028405e-66</v>
+        <v>1.175420132086748e-56</v>
       </c>
     </row>
     <row r="41">
@@ -18170,7 +18170,7 @@
         <v>8.914767699401844e-27</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0001604233699951622</v>
+        <v>0.000166152776066418</v>
       </c>
       <c r="I41" t="n">
         <v>5.232312852533308e-94</v>
@@ -18212,7 +18212,7 @@
         <v>1.929650886425778e-72</v>
       </c>
       <c r="V41" t="n">
-        <v>3.129273266989434e-104</v>
+        <v>1.568614120776844e-93</v>
       </c>
     </row>
     <row r="42">
@@ -18282,7 +18282,7 @@
         <v>0.5086493639812011</v>
       </c>
       <c r="V42" t="n">
-        <v>0.00263635691809818</v>
+        <v>0.01067641931264783</v>
       </c>
     </row>
     <row r="43">
@@ -18352,7 +18352,7 @@
         <v>0.9554415906005029</v>
       </c>
       <c r="V43" t="n">
-        <v>9.182315801621852e-12</v>
+        <v>9.403876586042311e-12</v>
       </c>
     </row>
     <row r="44">
@@ -18422,7 +18422,7 @@
         <v>1.324080124580137e-15</v>
       </c>
       <c r="V44" t="n">
-        <v>3.144300452287076e-16</v>
+        <v>9.198875118105574e-14</v>
       </c>
     </row>
     <row r="45">
@@ -18492,7 +18492,7 @@
         <v>8.054108762273412e-11</v>
       </c>
       <c r="V45" t="n">
-        <v>5.119977777852614e-27</v>
+        <v>1.47388710889028e-25</v>
       </c>
     </row>
     <row r="46">
@@ -18562,7 +18562,7 @@
         <v>0.009351581143357173</v>
       </c>
       <c r="V46" t="n">
-        <v>6.546204345990759e-05</v>
+        <v>9.25106771251553e-05</v>
       </c>
     </row>
     <row r="47">
@@ -18632,7 +18632,7 @@
         <v>0.4337772737387702</v>
       </c>
       <c r="V47" t="n">
-        <v>0.3757555715677249</v>
+        <v>0.5991005291286053</v>
       </c>
     </row>
     <row r="48">
@@ -18702,7 +18702,7 @@
         <v>0.006084901399856412</v>
       </c>
       <c r="V48" t="n">
-        <v>4.223876525806314e-12</v>
+        <v>1.229905602672938e-11</v>
       </c>
     </row>
     <row r="49">
@@ -18772,7 +18772,7 @@
         <v>0.0001267889191202726</v>
       </c>
       <c r="V49" t="n">
-        <v>8.081309807623488e-09</v>
+        <v>2.781998599761069e-07</v>
       </c>
     </row>
     <row r="50">
@@ -18842,7 +18842,7 @@
         <v>0.1086465722723773</v>
       </c>
       <c r="V50" t="n">
-        <v>0.514005895054685</v>
+        <v>0.3238053811473541</v>
       </c>
     </row>
     <row r="51">
@@ -18861,7 +18861,7 @@
         <v>0.00312547705384807</v>
       </c>
       <c r="E51" t="n">
-        <v>2.235175075632044e-44</v>
+        <v>2.407111619911432e-44</v>
       </c>
       <c r="F51" t="n">
         <v>1.713153825236178e-15</v>
@@ -18912,7 +18912,7 @@
         <v>1.393743525484966e-17</v>
       </c>
       <c r="V51" t="n">
-        <v>5.239313872403429e-155</v>
+        <v>8.729663919583314e-156</v>
       </c>
     </row>
     <row r="52">
@@ -18982,7 +18982,7 @@
         <v>9.109724104586926e-08</v>
       </c>
       <c r="V52" t="n">
-        <v>0.0001151086217898493</v>
+        <v>0.0001010708242778066</v>
       </c>
     </row>
     <row r="53">
@@ -19010,7 +19010,7 @@
         <v>0.01495342423829823</v>
       </c>
       <c r="H53" t="n">
-        <v>3.046132908033604e-05</v>
+        <v>3.184593494762403e-05</v>
       </c>
       <c r="I53" t="n">
         <v>1.577393054973708e-143</v>
@@ -19052,7 +19052,7 @@
         <v>5.588753806009892e-20</v>
       </c>
       <c r="V53" t="n">
-        <v>1.290584586017101e-60</v>
+        <v>4.106022259370455e-59</v>
       </c>
     </row>
     <row r="54">
@@ -19122,7 +19122,7 @@
         <v>3.984729950735546e-24</v>
       </c>
       <c r="V54" t="n">
-        <v>2.848572614612232e-35</v>
+        <v>2.494251586464111e-34</v>
       </c>
     </row>
     <row r="55">
@@ -19192,7 +19192,7 @@
         <v>4.517582262521941e-12</v>
       </c>
       <c r="V55" t="n">
-        <v>3.185170913967472e-79</v>
+        <v>1.392533424738425e-79</v>
       </c>
     </row>
     <row r="56">
@@ -19262,7 +19262,7 @@
         <v>2.979489810284672e-07</v>
       </c>
       <c r="V56" t="n">
-        <v>1.12840025096234e-08</v>
+        <v>2.965280366583526e-09</v>
       </c>
     </row>
     <row r="57">
@@ -19290,7 +19290,7 @@
         <v>2.459535705972988e-12</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0001093912161792352</v>
+        <v>0.0001137668648264046</v>
       </c>
       <c r="I57" t="n">
         <v>0.3737583572479912</v>
@@ -19332,7 +19332,7 @@
         <v>3.484747985253404e-67</v>
       </c>
       <c r="V57" t="n">
-        <v>3.919204810048266e-149</v>
+        <v>4.826065874504116e-132</v>
       </c>
     </row>
     <row r="58">
@@ -19402,7 +19402,7 @@
         <v>0.008825887525730275</v>
       </c>
       <c r="V58" t="n">
-        <v>2.69906986563455e-76</v>
+        <v>2.703616539920267e-74</v>
       </c>
     </row>
     <row r="59">
@@ -19421,7 +19421,7 @@
         <v>0.01477731546072067</v>
       </c>
       <c r="E59" t="n">
-        <v>3.8830041753264e-39</v>
+        <v>4.160361616421143e-39</v>
       </c>
       <c r="F59" t="n">
         <v>0.004734111274298094</v>
@@ -19430,7 +19430,7 @@
         <v>8.044821531469126e-09</v>
       </c>
       <c r="H59" t="n">
-        <v>3.160821863738295e-07</v>
+        <v>3.346752561605253e-07</v>
       </c>
       <c r="I59" t="n">
         <v>3.318723896175978e-247</v>
@@ -19472,7 +19472,7 @@
         <v>7.766417207566105e-64</v>
       </c>
       <c r="V59" t="n">
-        <v>4.205262215344467e-66</v>
+        <v>4.991708287488237e-56</v>
       </c>
     </row>
     <row r="60">
@@ -19542,7 +19542,7 @@
         <v>1.382405947377955e-05</v>
       </c>
       <c r="V60" t="n">
-        <v>0.00078463058731133</v>
+        <v>0.00803676834734268</v>
       </c>
     </row>
     <row r="61">
@@ -19561,7 +19561,7 @@
         <v>0.1510515842315964</v>
       </c>
       <c r="E61" t="n">
-        <v>4.005438586626734e-39</v>
+        <v>4.272467825735183e-39</v>
       </c>
       <c r="F61" t="n">
         <v>0.3274159287892248</v>
@@ -19612,7 +19612,7 @@
         <v>2.224260440462673e-28</v>
       </c>
       <c r="V61" t="n">
-        <v>1.826451982979684e-128</v>
+        <v>3.076732365872305e-130</v>
       </c>
     </row>
     <row r="62">
@@ -19628,7 +19628,7 @@
         <v>1.460029942243725e-27</v>
       </c>
       <c r="D62" t="n">
-        <v>8.563791684596663e-27</v>
+        <v>9.099028664883955e-27</v>
       </c>
       <c r="E62" t="n">
         <v>7.948883406917228e-58</v>
@@ -19652,13 +19652,13 @@
         <v>9.491834246648477e-54</v>
       </c>
       <c r="L62" t="n">
-        <v>4.682854426473563e-20</v>
+        <v>5.151139869120919e-20</v>
       </c>
       <c r="M62" t="n">
         <v>5.180973120332964e-313</v>
       </c>
       <c r="N62" t="n">
-        <v>1.047898144237426e-75</v>
+        <v>1.178885412267104e-75</v>
       </c>
       <c r="O62" t="n">
         <v>7.478340342234645e-168</v>
@@ -19670,10 +19670,10 @@
         <v>6.170123668987718e-17</v>
       </c>
       <c r="R62" t="n">
-        <v>5.319971316080557e-25</v>
+        <v>5.803605072087879e-25</v>
       </c>
       <c r="S62" t="n">
-        <v>1.346220974782754e-15</v>
+        <v>1.570591137246546e-15</v>
       </c>
       <c r="T62" t="n">
         <v>1.785415095505448e-182</v>
@@ -19752,7 +19752,7 @@
         <v>0.3702057975719203</v>
       </c>
       <c r="V63" t="n">
-        <v>9.355530638358908e-13</v>
+        <v>2.700903377993806e-12</v>
       </c>
     </row>
     <row r="64">
@@ -19768,7 +19768,7 @@
         <v>8.857061664858655e-23</v>
       </c>
       <c r="D64" t="n">
-        <v>3.960127380478209e-31</v>
+        <v>4.242993621940938e-31</v>
       </c>
       <c r="E64" t="n">
         <v>2.240259620668116e-19</v>
@@ -19780,7 +19780,7 @@
         <v>1.321384808908717e-59</v>
       </c>
       <c r="H64" t="n">
-        <v>6.764916610033225e-05</v>
+        <v>7.046788135451276e-05</v>
       </c>
       <c r="I64" t="n">
         <v>6.236410045415442e-128</v>
@@ -19789,13 +19789,13 @@
         <v>1.698720020224418e-100</v>
       </c>
       <c r="K64" t="n">
-        <v>8.215644947842075e-18</v>
+        <v>8.69891818006808e-18</v>
       </c>
       <c r="L64" t="n">
         <v>4.273209539292244e-13</v>
       </c>
       <c r="M64" t="n">
-        <v>5.752876731517829e-143</v>
+        <v>6.392085257242032e-143</v>
       </c>
       <c r="N64" t="n">
         <v>2.198505228262436e-46</v>
@@ -19822,7 +19822,7 @@
         <v>3.93853392885556e-144</v>
       </c>
       <c r="V64" t="n">
-        <v>5.997250014948354e-252</v>
+        <v>3.008330799901067e-237</v>
       </c>
     </row>
     <row r="65">
@@ -19892,7 +19892,7 @@
         <v>7.214373168565874e-60</v>
       </c>
       <c r="V65" t="n">
-        <v>2.680564869855248e-310</v>
+        <v>3.670245114763141e-303</v>
       </c>
     </row>
     <row r="66">
@@ -19990,7 +19990,7 @@
         <v>3.307341846557821e-57</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0001575488099827657</v>
+        <v>0.0001633839510932385</v>
       </c>
       <c r="I67" t="n">
         <v>5.085335947801273e-14</v>
@@ -20032,7 +20032,7 @@
         <v>1.94076887199054e-45</v>
       </c>
       <c r="V67" t="n">
-        <v>2.274760145171257e-34</v>
+        <v>2.130145663292947e-32</v>
       </c>
     </row>
     <row r="68">
@@ -20102,7 +20102,7 @@
         <v>7.378055754508842e-20</v>
       </c>
       <c r="V68" t="n">
-        <v>1.740173420636603e-300</v>
+        <v>9.762443742729287e-298</v>
       </c>
     </row>
     <row r="69">
@@ -20242,7 +20242,7 @@
         <v>0.05624085969133212</v>
       </c>
       <c r="V70" t="n">
-        <v>5.739691868649158e-19</v>
+        <v>7.693587660452188e-18</v>
       </c>
     </row>
     <row r="71">
@@ -20282,13 +20282,13 @@
         <v>2.17815873191753e-05</v>
       </c>
       <c r="L71" t="n">
-        <v>1.854161456735346e-18</v>
+        <v>2.008674911463291e-18</v>
       </c>
       <c r="M71" t="n">
         <v>5.961378852971182e-81</v>
       </c>
       <c r="N71" t="n">
-        <v>2.953761230680627e-72</v>
+        <v>3.281956922978475e-72</v>
       </c>
       <c r="O71" t="n">
         <v>2.379010192955319e-86</v>
@@ -20312,7 +20312,7 @@
         <v>2.411110658579214e-24</v>
       </c>
       <c r="V71" t="n">
-        <v>1.470970799467753e-134</v>
+        <v>1.579837580035308e-105</v>
       </c>
     </row>
     <row r="72">
@@ -20382,7 +20382,7 @@
         <v>0.1374161021627483</v>
       </c>
       <c r="V72" t="n">
-        <v>0.0001301521767260473</v>
+        <v>7.843873632006938e-05</v>
       </c>
     </row>
     <row r="73">
@@ -20452,7 +20452,7 @@
         <v>1</v>
       </c>
       <c r="V73" t="n">
-        <v>3.670705567405607e-07</v>
+        <v>9.333963892401457e-08</v>
       </c>
     </row>
     <row r="74">
@@ -20522,7 +20522,7 @@
         <v>0.2043216431414838</v>
       </c>
       <c r="V74" t="n">
-        <v>3.438907834043951e-65</v>
+        <v>8.238467433267367e-69</v>
       </c>
     </row>
     <row r="75">
@@ -20535,7 +20535,7 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>1.759080849529393e-61</v>
+        <v>2.010378113747877e-61</v>
       </c>
       <c r="D75" t="n">
         <v>4.150764664636786e-61</v>
@@ -20550,7 +20550,7 @@
         <v>1.056784843167148e-200</v>
       </c>
       <c r="H75" t="n">
-        <v>2.073541011866624e-07</v>
+        <v>2.211777079324399e-07</v>
       </c>
       <c r="I75" t="n">
         <v>1.130750976709597e-20</v>
@@ -20562,10 +20562,10 @@
         <v>2.286482137306865e-13</v>
       </c>
       <c r="L75" t="n">
-        <v>1.038979228371485e-20</v>
+        <v>1.168851631917921e-20</v>
       </c>
       <c r="M75" t="n">
-        <v>3.805230402641546e-138</v>
+        <v>4.151160439245321e-138</v>
       </c>
       <c r="N75" t="n">
         <v>3.207347857495513e-141</v>
@@ -20583,7 +20583,7 @@
         <v>1.123753937656048e-08</v>
       </c>
       <c r="S75" t="n">
-        <v>3.192572648255191e-14</v>
+        <v>3.64865445514879e-14</v>
       </c>
       <c r="T75" t="n">
         <v>7.101483297622377e-74</v>
@@ -20620,7 +20620,7 @@
         <v>6.245133534252855e-08</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0002477805428539571</v>
+        <v>0.0002563246995040935</v>
       </c>
       <c r="I76" t="n">
         <v>2.407458832127236e-10</v>
@@ -20662,7 +20662,7 @@
         <v>8.96474772568168e-43</v>
       </c>
       <c r="V76" t="n">
-        <v>2.075031543531163e-20</v>
+        <v>2.022081481850475e-13</v>
       </c>
     </row>
     <row r="77">
@@ -20702,7 +20702,7 @@
         <v>0.008994370218054265</v>
       </c>
       <c r="L77" t="n">
-        <v>1.060171601288823e-19</v>
+        <v>1.156550837769625e-19</v>
       </c>
       <c r="M77" t="n">
         <v>0.007325715153450653</v>
@@ -20732,7 +20732,7 @@
         <v>2.489518997344314e-08</v>
       </c>
       <c r="V77" t="n">
-        <v>3.020456174594747e-100</v>
+        <v>9.447517010935856e-122</v>
       </c>
     </row>
     <row r="78">
@@ -20802,7 +20802,7 @@
         <v>2.976810925724367e-19</v>
       </c>
       <c r="V78" t="n">
-        <v>0.001705760101893513</v>
+        <v>0.0013687243942494</v>
       </c>
     </row>
     <row r="79">
@@ -20872,7 +20872,7 @@
         <v>0.02838639389934005</v>
       </c>
       <c r="V79" t="n">
-        <v>1.154584785881989e-22</v>
+        <v>2.154325195276577e-17</v>
       </c>
     </row>
     <row r="80">
@@ -20942,7 +20942,7 @@
         <v>4.420128576570046e-132</v>
       </c>
       <c r="V80" t="n">
-        <v>1.925374038448796e-173</v>
+        <v>7.978948804405207e-149</v>
       </c>
     </row>
     <row r="81">
@@ -21012,7 +21012,7 @@
         <v>2.629136192655611e-233</v>
       </c>
       <c r="V81" t="n">
-        <v>2.077684107048298e-17</v>
+        <v>1.995304606214018e-11</v>
       </c>
     </row>
     <row r="82">
@@ -21055,7 +21055,7 @@
         <v>4.324534368321413e-27</v>
       </c>
       <c r="M82" t="n">
-        <v>2.947597094253136e-132</v>
+        <v>3.193230185440898e-132</v>
       </c>
       <c r="N82" t="n">
         <v>2.941224738544289e-12</v>
@@ -21134,7 +21134,7 @@
         <v>9.634145825709727e-09</v>
       </c>
       <c r="P83" t="n">
-        <v>4.526391847353296e-31</v>
+        <v>5.029324274836995e-31</v>
       </c>
       <c r="Q83" t="n">
         <v>1.072310869689949e-72</v>
@@ -21152,7 +21152,7 @@
         <v>1.059529644714957e-63</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.414427709068624e-266</v>
       </c>
     </row>
     <row r="84">
@@ -21222,7 +21222,7 @@
         <v>1.423933940769116e-218</v>
       </c>
       <c r="V84" t="n">
-        <v>5.864594887627989e-171</v>
+        <v>6.081067713992006e-72</v>
       </c>
     </row>
     <row r="85">
@@ -21292,7 +21292,7 @@
         <v>4.410985516306592e-72</v>
       </c>
       <c r="V85" t="n">
-        <v>5.262894821729112e-16</v>
+        <v>5.001646963209778e-11</v>
       </c>
     </row>
     <row r="86">
@@ -21362,7 +21362,7 @@
         <v>6.290544715445595e-09</v>
       </c>
       <c r="V86" t="n">
-        <v>8.171949442661347e-06</v>
+        <v>7.209021736296078e-07</v>
       </c>
     </row>
     <row r="87">
@@ -21432,7 +21432,7 @@
         <v>1.859557762894373e-08</v>
       </c>
       <c r="V87" t="n">
-        <v>0.7852874087182713</v>
+        <v>0.1470148202513763</v>
       </c>
     </row>
     <row r="88">
@@ -21469,7 +21469,7 @@
         <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>1.490917962283398e-20</v>
+        <v>1.58410033492611e-20</v>
       </c>
       <c r="L88" t="n">
         <v>0.4937359423091974</v>
@@ -21502,7 +21502,7 @@
         <v>0.2810635789348018</v>
       </c>
       <c r="V88" t="n">
-        <v>1.221764795221158e-06</v>
+        <v>1.067147025989507e-07</v>
       </c>
     </row>
     <row r="89">
@@ -21572,7 +21572,7 @@
         <v>1</v>
       </c>
       <c r="V89" t="n">
-        <v>0.1306717775439525</v>
+        <v>0.2082841919889568</v>
       </c>
     </row>
     <row r="90">
@@ -21642,7 +21642,7 @@
         <v>1.053046060122974e-17</v>
       </c>
       <c r="V90" t="n">
-        <v>3.55563895745573e-10</v>
+        <v>2.667779481585692e-13</v>
       </c>
     </row>
     <row r="91">
@@ -21712,7 +21712,7 @@
         <v>0.7955523260792448</v>
       </c>
       <c r="V91" t="n">
-        <v>0.0001457409697566889</v>
+        <v>0.00587855740716903</v>
       </c>
     </row>
     <row r="92">
@@ -21782,7 +21782,7 @@
         <v>0.04132873990955606</v>
       </c>
       <c r="V92" t="n">
-        <v>1</v>
+        <v>0.4893160641545008</v>
       </c>
     </row>
     <row r="93">
@@ -21852,7 +21852,7 @@
         <v>0.09127009089527477</v>
       </c>
       <c r="V93" t="n">
-        <v>7.101211061193528e-06</v>
+        <v>1.371415763797975e-05</v>
       </c>
     </row>
     <row r="94">
@@ -21922,7 +21922,7 @@
         <v>1</v>
       </c>
       <c r="V94" t="n">
-        <v>0.00439391990927377</v>
+        <v>0.003182212180704711</v>
       </c>
     </row>
     <row r="95">
@@ -21992,7 +21992,7 @@
         <v>0.0202147560866792</v>
       </c>
       <c r="V95" t="n">
-        <v>0.004470993833643693</v>
+        <v>0.008321433039693045</v>
       </c>
     </row>
     <row r="96">
@@ -22062,7 +22062,7 @@
         <v>0.007499666805138027</v>
       </c>
       <c r="V96" t="n">
-        <v>0.9350053099669408</v>
+        <v>0.8501986263944209</v>
       </c>
     </row>
     <row r="97">
@@ -22132,7 +22132,7 @@
         <v>1</v>
       </c>
       <c r="V97" t="n">
-        <v>0.3010001199629554</v>
+        <v>0.2739030688057575</v>
       </c>
     </row>
     <row r="98">
@@ -22202,7 +22202,7 @@
         <v>0.793766643349229</v>
       </c>
       <c r="V98" t="n">
-        <v>0.2396973061700864</v>
+        <v>0.4630259563014836</v>
       </c>
     </row>
     <row r="99">
@@ -22272,7 +22272,7 @@
         <v>1</v>
       </c>
       <c r="V99" t="n">
-        <v>0.001195010830594409</v>
+        <v>0.00157616890543965</v>
       </c>
     </row>
     <row r="100">
@@ -22342,7 +22342,7 @@
         <v>0.3672999724623839</v>
       </c>
       <c r="V100" t="n">
-        <v>0.0002078043187512631</v>
+        <v>0.0001006615552734729</v>
       </c>
     </row>
     <row r="101">
@@ -22400,7 +22400,7 @@
         <v>0.2093247466822352</v>
       </c>
       <c r="R101" t="n">
-        <v>3.76702678806498e-25</v>
+        <v>4.1855853200722e-25</v>
       </c>
       <c r="S101" t="n">
         <v>0.1267071396182306</v>
@@ -22412,7 +22412,7 @@
         <v>9.161209408007459e-54</v>
       </c>
       <c r="V101" t="n">
-        <v>5.566734737653119e-117</v>
+        <v>3.608730403445818e-71</v>
       </c>
     </row>
     <row r="102">
@@ -22482,7 +22482,7 @@
         <v>8.688473559604855e-12</v>
       </c>
       <c r="V102" t="n">
-        <v>3.347189953982757e-39</v>
+        <v>1.014106670051302e-22</v>
       </c>
     </row>
     <row r="103">
@@ -22552,7 +22552,7 @@
         <v>0.5626450053783794</v>
       </c>
       <c r="V103" t="n">
-        <v>7.101211061193528e-06</v>
+        <v>4.75812762648954e-06</v>
       </c>
     </row>
     <row r="104">
@@ -22580,7 +22580,7 @@
         <v>6.689882554908918e-179</v>
       </c>
       <c r="H104" t="n">
-        <v>3.046132908033604e-05</v>
+        <v>3.184593494762403e-05</v>
       </c>
       <c r="I104" t="n">
         <v>0.3143386919791346</v>
@@ -22598,7 +22598,7 @@
         <v>9.310565154614237e-78</v>
       </c>
       <c r="N104" t="n">
-        <v>1.541860473000143e-70</v>
+        <v>1.682029606909246e-70</v>
       </c>
       <c r="O104" t="n">
         <v>1.92857935615977e-122</v>
@@ -22610,7 +22610,7 @@
         <v>0.2093247466822352</v>
       </c>
       <c r="R104" t="n">
-        <v>2.597477634965458e-24</v>
+        <v>2.813934104545913e-24</v>
       </c>
       <c r="S104" t="n">
         <v>0.361732069311574</v>
@@ -22622,7 +22622,7 @@
         <v>4.557072371348927e-84</v>
       </c>
       <c r="V104" t="n">
-        <v>3.197620048708951e-159</v>
+        <v>7.862393588052323e-80</v>
       </c>
     </row>
   </sheetData>
@@ -22818,7 +22818,7 @@
         <v>81</v>
       </c>
       <c r="V2" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -22888,7 +22888,7 @@
         <v>830</v>
       </c>
       <c r="V3" t="n">
-        <v>1971</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="4">
@@ -22958,7 +22958,7 @@
         <v>468</v>
       </c>
       <c r="V4" t="n">
-        <v>286</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5">
@@ -23028,7 +23028,7 @@
         <v>6984</v>
       </c>
       <c r="V5" t="n">
-        <v>3866</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="6">
@@ -23098,7 +23098,7 @@
         <v>236</v>
       </c>
       <c r="V6" t="n">
-        <v>83</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -23168,7 +23168,7 @@
         <v>175</v>
       </c>
       <c r="V7" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8">
@@ -23238,7 +23238,7 @@
         <v>1426</v>
       </c>
       <c r="V8" t="n">
-        <v>2372</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="9">
@@ -23308,7 +23308,7 @@
         <v>688</v>
       </c>
       <c r="V9" t="n">
-        <v>859</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10">
@@ -23378,7 +23378,7 @@
         <v>994</v>
       </c>
       <c r="V10" t="n">
-        <v>978</v>
+        <v>833</v>
       </c>
     </row>
     <row r="11">
@@ -23448,7 +23448,7 @@
         <v>4234</v>
       </c>
       <c r="V11" t="n">
-        <v>3588</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="12">
@@ -23518,7 +23518,7 @@
         <v>3749</v>
       </c>
       <c r="V12" t="n">
-        <v>2761</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="13">
@@ -23588,7 +23588,7 @@
         <v>2526</v>
       </c>
       <c r="V13" t="n">
-        <v>2141</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="14">
@@ -23658,7 +23658,7 @@
         <v>1035</v>
       </c>
       <c r="V14" t="n">
-        <v>1456</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="15">
@@ -23668,67 +23668,67 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2996</v>
+        <v>4234</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="E15" t="n">
+        <v>47</v>
+      </c>
+      <c r="F15" t="n">
+        <v>119</v>
+      </c>
+      <c r="G15" t="n">
+        <v>175</v>
+      </c>
+      <c r="H15" t="n">
         <v>25</v>
       </c>
-      <c r="F15" t="n">
-        <v>108</v>
-      </c>
-      <c r="G15" t="n">
-        <v>142</v>
-      </c>
-      <c r="H15" t="n">
-        <v>15</v>
-      </c>
       <c r="I15" t="n">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="J15" t="n">
-        <v>462</v>
+        <v>555</v>
       </c>
       <c r="K15" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="L15" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="M15" t="n">
-        <v>253</v>
+        <v>572</v>
       </c>
       <c r="N15" t="n">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="O15" t="n">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="P15" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="Q15" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R15" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="S15" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="T15" t="n">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="U15" t="n">
-        <v>245</v>
+        <v>338</v>
       </c>
       <c r="V15" t="n">
-        <v>542</v>
+        <v>734</v>
       </c>
     </row>
     <row r="16">
@@ -23798,7 +23798,7 @@
         <v>407</v>
       </c>
       <c r="V16" t="n">
-        <v>942</v>
+        <v>886</v>
       </c>
     </row>
     <row r="17">
@@ -23868,7 +23868,7 @@
         <v>788</v>
       </c>
       <c r="V17" t="n">
-        <v>778</v>
+        <v>652</v>
       </c>
     </row>
     <row r="18">
@@ -23938,7 +23938,7 @@
         <v>5149</v>
       </c>
       <c r="V18" t="n">
-        <v>2978</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="19">
@@ -24008,7 +24008,7 @@
         <v>5538</v>
       </c>
       <c r="V19" t="n">
-        <v>6055</v>
+        <v>5358</v>
       </c>
     </row>
     <row r="20">
@@ -24078,7 +24078,7 @@
         <v>1184</v>
       </c>
       <c r="V20" t="n">
-        <v>1073</v>
+        <v>923</v>
       </c>
     </row>
     <row r="21">
@@ -24148,7 +24148,7 @@
         <v>337</v>
       </c>
       <c r="V21" t="n">
-        <v>266</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22">
@@ -24218,7 +24218,7 @@
         <v>796</v>
       </c>
       <c r="V22" t="n">
-        <v>741</v>
+        <v>679</v>
       </c>
     </row>
     <row r="23">
@@ -24288,7 +24288,7 @@
         <v>468</v>
       </c>
       <c r="V23" t="n">
-        <v>471</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24">
@@ -24358,7 +24358,7 @@
         <v>342</v>
       </c>
       <c r="V24" t="n">
-        <v>311</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25">
@@ -24428,7 +24428,7 @@
         <v>852</v>
       </c>
       <c r="V25" t="n">
-        <v>954</v>
+        <v>886</v>
       </c>
     </row>
     <row r="26">
@@ -24498,7 +24498,7 @@
         <v>242</v>
       </c>
       <c r="V26" t="n">
-        <v>242</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27">
@@ -24568,7 +24568,7 @@
         <v>48</v>
       </c>
       <c r="V27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
@@ -24638,7 +24638,7 @@
         <v>277</v>
       </c>
       <c r="V28" t="n">
-        <v>273</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29">
@@ -24708,7 +24708,7 @@
         <v>208</v>
       </c>
       <c r="V29" t="n">
-        <v>231</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30">
@@ -24778,7 +24778,7 @@
         <v>56</v>
       </c>
       <c r="V30" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
@@ -24848,7 +24848,7 @@
         <v>295</v>
       </c>
       <c r="V31" t="n">
-        <v>384</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32">
@@ -24918,7 +24918,7 @@
         <v>460</v>
       </c>
       <c r="V32" t="n">
-        <v>403</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33">
@@ -24988,7 +24988,7 @@
         <v>250</v>
       </c>
       <c r="V33" t="n">
-        <v>217</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34">
@@ -25058,7 +25058,7 @@
         <v>281</v>
       </c>
       <c r="V34" t="n">
-        <v>244</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35">
@@ -25128,7 +25128,7 @@
         <v>580</v>
       </c>
       <c r="V35" t="n">
-        <v>517</v>
+        <v>477</v>
       </c>
     </row>
     <row r="36">
@@ -25198,7 +25198,7 @@
         <v>92</v>
       </c>
       <c r="V36" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37">
@@ -25268,7 +25268,7 @@
         <v>367</v>
       </c>
       <c r="V37" t="n">
-        <v>468</v>
+        <v>429</v>
       </c>
     </row>
     <row r="38">
@@ -25338,7 +25338,7 @@
         <v>194</v>
       </c>
       <c r="V38" t="n">
-        <v>211</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39">
@@ -25408,7 +25408,7 @@
         <v>101</v>
       </c>
       <c r="V39" t="n">
-        <v>202</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40">
@@ -25478,7 +25478,7 @@
         <v>374</v>
       </c>
       <c r="V40" t="n">
-        <v>461</v>
+        <v>431</v>
       </c>
     </row>
     <row r="41">
@@ -25548,7 +25548,7 @@
         <v>200</v>
       </c>
       <c r="V41" t="n">
-        <v>305</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42">
@@ -25618,7 +25618,7 @@
         <v>94</v>
       </c>
       <c r="V42" t="n">
-        <v>168</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43">
@@ -25688,7 +25688,7 @@
         <v>426</v>
       </c>
       <c r="V43" t="n">
-        <v>622</v>
+        <v>572</v>
       </c>
     </row>
     <row r="44">
@@ -25758,7 +25758,7 @@
         <v>206</v>
       </c>
       <c r="V44" t="n">
-        <v>235</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45">
@@ -25828,7 +25828,7 @@
         <v>99</v>
       </c>
       <c r="V45" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46">
@@ -25898,7 +25898,7 @@
         <v>175</v>
       </c>
       <c r="V46" t="n">
-        <v>226</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47">
@@ -25968,7 +25968,7 @@
         <v>274</v>
       </c>
       <c r="V47" t="n">
-        <v>353</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48">
@@ -26038,7 +26038,7 @@
         <v>134</v>
       </c>
       <c r="V48" t="n">
-        <v>160</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49">
@@ -26108,7 +26108,7 @@
         <v>206</v>
       </c>
       <c r="V49" t="n">
-        <v>275</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50">
@@ -26178,7 +26178,7 @@
         <v>597</v>
       </c>
       <c r="V50" t="n">
-        <v>730</v>
+        <v>675</v>
       </c>
     </row>
     <row r="51">
@@ -26248,7 +26248,7 @@
         <v>227</v>
       </c>
       <c r="V51" t="n">
-        <v>547</v>
+        <v>520</v>
       </c>
     </row>
     <row r="52">
@@ -26318,7 +26318,7 @@
         <v>390</v>
       </c>
       <c r="V52" t="n">
-        <v>634</v>
+        <v>569</v>
       </c>
     </row>
     <row r="53">
@@ -26388,7 +26388,7 @@
         <v>629</v>
       </c>
       <c r="V53" t="n">
-        <v>849</v>
+        <v>787</v>
       </c>
     </row>
     <row r="54">
@@ -26458,7 +26458,7 @@
         <v>443</v>
       </c>
       <c r="V54" t="n">
-        <v>469</v>
+        <v>434</v>
       </c>
     </row>
     <row r="55">
@@ -26528,7 +26528,7 @@
         <v>115</v>
       </c>
       <c r="V55" t="n">
-        <v>269</v>
+        <v>257</v>
       </c>
     </row>
     <row r="56">
@@ -26598,7 +26598,7 @@
         <v>3979</v>
       </c>
       <c r="V56" t="n">
-        <v>3816</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="57">
@@ -26668,7 +26668,7 @@
         <v>1126</v>
       </c>
       <c r="V57" t="n">
-        <v>1215</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="58">
@@ -26738,7 +26738,7 @@
         <v>2030</v>
       </c>
       <c r="V58" t="n">
-        <v>1947</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="59">
@@ -26808,7 +26808,7 @@
         <v>1389</v>
       </c>
       <c r="V59" t="n">
-        <v>1969</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="60">
@@ -26878,7 +26878,7 @@
         <v>1094</v>
       </c>
       <c r="V60" t="n">
-        <v>1368</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="61">
@@ -26948,7 +26948,7 @@
         <v>2401</v>
       </c>
       <c r="V61" t="n">
-        <v>3498</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="62">
@@ -27018,7 +27018,7 @@
         <v>2818</v>
       </c>
       <c r="V62" t="n">
-        <v>2922</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="63">
@@ -27088,7 +27088,7 @@
         <v>4752</v>
       </c>
       <c r="V63" t="n">
-        <v>5259</v>
+        <v>4777</v>
       </c>
     </row>
     <row r="64">
@@ -27158,7 +27158,7 @@
         <v>3004</v>
       </c>
       <c r="V64" t="n">
-        <v>3373</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="65">
@@ -27228,7 +27228,7 @@
         <v>1445</v>
       </c>
       <c r="V65" t="n">
-        <v>2259</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="66">
@@ -27298,7 +27298,7 @@
         <v>10203</v>
       </c>
       <c r="V66" t="n">
-        <v>8428</v>
+        <v>7432</v>
       </c>
     </row>
     <row r="67">
@@ -27368,7 +27368,7 @@
         <v>895</v>
       </c>
       <c r="V67" t="n">
-        <v>692</v>
+        <v>620</v>
       </c>
     </row>
     <row r="68">
@@ -27438,7 +27438,7 @@
         <v>90</v>
       </c>
       <c r="V68" t="n">
-        <v>529</v>
+        <v>504</v>
       </c>
     </row>
     <row r="69">
@@ -27508,7 +27508,7 @@
         <v>10725</v>
       </c>
       <c r="V69" t="n">
-        <v>8951</v>
+        <v>7878</v>
       </c>
     </row>
     <row r="70">
@@ -27578,7 +27578,7 @@
         <v>6</v>
       </c>
       <c r="V70" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71">
@@ -27648,7 +27648,7 @@
         <v>194</v>
       </c>
       <c r="V71" t="n">
-        <v>276</v>
+        <v>213</v>
       </c>
     </row>
     <row r="72">
@@ -27858,7 +27858,7 @@
         <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="75">
@@ -27928,7 +27928,7 @@
         <v>125</v>
       </c>
       <c r="V75" t="n">
-        <v>376</v>
+        <v>369</v>
       </c>
     </row>
     <row r="76">
@@ -27998,7 +27998,7 @@
         <v>437</v>
       </c>
       <c r="V76" t="n">
-        <v>696</v>
+        <v>594</v>
       </c>
     </row>
     <row r="77">
@@ -28068,7 +28068,7 @@
         <v>275</v>
       </c>
       <c r="V77" t="n">
-        <v>1956</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="78">
@@ -28138,7 +28138,7 @@
         <v>127</v>
       </c>
       <c r="V78" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79">
@@ -28208,7 +28208,7 @@
         <v>21</v>
       </c>
       <c r="V79" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="80">
@@ -28278,7 +28278,7 @@
         <v>28</v>
       </c>
       <c r="V80" t="n">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="81">
@@ -28348,7 +28348,7 @@
         <v>2699</v>
       </c>
       <c r="V81" t="n">
-        <v>743</v>
+        <v>725</v>
       </c>
     </row>
     <row r="82">
@@ -28418,7 +28418,7 @@
         <v>1749</v>
       </c>
       <c r="V82" t="n">
-        <v>3767</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="83">
@@ -28488,7 +28488,7 @@
         <v>6343</v>
       </c>
       <c r="V83" t="n">
-        <v>3728</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="84">
@@ -28558,7 +28558,7 @@
         <v>4136</v>
       </c>
       <c r="V84" t="n">
-        <v>866</v>
+        <v>524</v>
       </c>
     </row>
     <row r="85">
@@ -28628,7 +28628,7 @@
         <v>546</v>
       </c>
       <c r="V85" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86">
@@ -28698,7 +28698,7 @@
         <v>19</v>
       </c>
       <c r="V86" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="87">
@@ -28768,7 +28768,7 @@
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="88">
@@ -28978,7 +28978,7 @@
         <v>11994</v>
       </c>
       <c r="V90" t="n">
-        <v>13451</v>
+        <v>12204</v>
       </c>
     </row>
     <row r="91">
@@ -29048,7 +29048,7 @@
         <v>6</v>
       </c>
       <c r="V91" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92">
@@ -29118,7 +29118,7 @@
         <v>15</v>
       </c>
       <c r="V92" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="93">
@@ -29188,7 +29188,7 @@
         <v>106</v>
       </c>
       <c r="V93" t="n">
-        <v>199</v>
+        <v>178</v>
       </c>
     </row>
     <row r="94">
@@ -29328,7 +29328,7 @@
         <v>13</v>
       </c>
       <c r="V95" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="96">
@@ -29608,7 +29608,7 @@
         <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100">
@@ -29678,7 +29678,7 @@
         <v>26</v>
       </c>
       <c r="V100" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="101">
@@ -29748,7 +29748,7 @@
         <v>440</v>
       </c>
       <c r="V101" t="n">
-        <v>469</v>
+        <v>325</v>
       </c>
     </row>
     <row r="102">
@@ -29818,7 +29818,7 @@
         <v>96</v>
       </c>
       <c r="V102" t="n">
-        <v>147</v>
+        <v>97</v>
       </c>
     </row>
     <row r="103">
@@ -29958,7 +29958,7 @@
         <v>789</v>
       </c>
       <c r="V104" t="n">
-        <v>625</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -30154,7 +30154,7 @@
         <v>40</v>
       </c>
       <c r="V2" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
@@ -30224,7 +30224,7 @@
         <v>499</v>
       </c>
       <c r="V3" t="n">
-        <v>2372</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="4">
@@ -30294,7 +30294,7 @@
         <v>207</v>
       </c>
       <c r="V4" t="n">
-        <v>607</v>
+        <v>572</v>
       </c>
     </row>
     <row r="5">
@@ -30364,7 +30364,7 @@
         <v>3162</v>
       </c>
       <c r="V5" t="n">
-        <v>7614</v>
+        <v>7126</v>
       </c>
     </row>
     <row r="6">
@@ -30434,7 +30434,7 @@
         <v>56</v>
       </c>
       <c r="V6" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -30504,7 +30504,7 @@
         <v>266</v>
       </c>
       <c r="V7" t="n">
-        <v>1237</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="8">
@@ -30574,7 +30574,7 @@
         <v>3020</v>
       </c>
       <c r="V8" t="n">
-        <v>15625</v>
+        <v>15201</v>
       </c>
     </row>
     <row r="9">
@@ -30644,7 +30644,7 @@
         <v>426</v>
       </c>
       <c r="V9" t="n">
-        <v>1530</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="10">
@@ -30714,7 +30714,7 @@
         <v>606</v>
       </c>
       <c r="V10" t="n">
-        <v>2149</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="11">
@@ -30784,7 +30784,7 @@
         <v>685</v>
       </c>
       <c r="V11" t="n">
-        <v>1892</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="12">
@@ -30854,7 +30854,7 @@
         <v>1200</v>
       </c>
       <c r="V12" t="n">
-        <v>3119</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="13">
@@ -30924,7 +30924,7 @@
         <v>2079</v>
       </c>
       <c r="V13" t="n">
-        <v>6296</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="14">
@@ -30994,7 +30994,7 @@
         <v>2718</v>
       </c>
       <c r="V14" t="n">
-        <v>12032</v>
+        <v>11586</v>
       </c>
     </row>
     <row r="15">
@@ -31004,67 +31004,67 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24455</v>
+        <v>24625</v>
       </c>
       <c r="C15" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D15" t="n">
-        <v>979</v>
+        <v>988</v>
       </c>
       <c r="E15" t="n">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F15" t="n">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="G15" t="n">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H15" t="n">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="I15" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="J15" t="n">
-        <v>2654</v>
+        <v>2672</v>
       </c>
       <c r="K15" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="L15" t="n">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="M15" t="n">
-        <v>1089</v>
+        <v>1103</v>
       </c>
       <c r="N15" t="n">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="O15" t="n">
-        <v>2058</v>
+        <v>2072</v>
       </c>
       <c r="P15" t="n">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="Q15" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R15" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S15" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="T15" t="n">
-        <v>1046</v>
+        <v>1055</v>
       </c>
       <c r="U15" t="n">
-        <v>1589</v>
+        <v>1600</v>
       </c>
       <c r="V15" t="n">
-        <v>7902</v>
+        <v>7723</v>
       </c>
     </row>
     <row r="16">
@@ -31134,7 +31134,7 @@
         <v>2985</v>
       </c>
       <c r="V16" t="n">
-        <v>14405</v>
+        <v>14059</v>
       </c>
     </row>
     <row r="17">
@@ -31204,7 +31204,7 @@
         <v>893</v>
       </c>
       <c r="V17" t="n">
-        <v>3770</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="18">
@@ -31274,7 +31274,7 @@
         <v>2336</v>
       </c>
       <c r="V18" t="n">
-        <v>6371</v>
+        <v>6041</v>
       </c>
     </row>
     <row r="19">
@@ -31344,7 +31344,7 @@
         <v>2068</v>
       </c>
       <c r="V19" t="n">
-        <v>6755</v>
+        <v>6247</v>
       </c>
     </row>
     <row r="20">
@@ -31414,7 +31414,7 @@
         <v>1981</v>
       </c>
       <c r="V20" t="n">
-        <v>7219</v>
+        <v>6979</v>
       </c>
     </row>
     <row r="21">
@@ -31484,7 +31484,7 @@
         <v>157</v>
       </c>
       <c r="V21" t="n">
-        <v>536</v>
+        <v>514</v>
       </c>
     </row>
     <row r="22">
@@ -31554,7 +31554,7 @@
         <v>752</v>
       </c>
       <c r="V22" t="n">
-        <v>2944</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="23">
@@ -31624,7 +31624,7 @@
         <v>48</v>
       </c>
       <c r="V23" t="n">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24">
@@ -31694,7 +31694,7 @@
         <v>61</v>
       </c>
       <c r="V24" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25">
@@ -31764,7 +31764,7 @@
         <v>159</v>
       </c>
       <c r="V25" t="n">
-        <v>814</v>
+        <v>789</v>
       </c>
     </row>
     <row r="26">
@@ -31834,7 +31834,7 @@
         <v>118</v>
       </c>
       <c r="V26" t="n">
-        <v>409</v>
+        <v>387</v>
       </c>
     </row>
     <row r="27">
@@ -31904,7 +31904,7 @@
         <v>21</v>
       </c>
       <c r="V27" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28">
@@ -31974,7 +31974,7 @@
         <v>23</v>
       </c>
       <c r="V28" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29">
@@ -32044,7 +32044,7 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30">
@@ -32114,7 +32114,7 @@
         <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
@@ -32184,7 +32184,7 @@
         <v>74</v>
       </c>
       <c r="V31" t="n">
-        <v>335</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32">
@@ -32254,7 +32254,7 @@
         <v>586</v>
       </c>
       <c r="V32" t="n">
-        <v>2880</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="33">
@@ -32324,7 +32324,7 @@
         <v>67</v>
       </c>
       <c r="V33" t="n">
-        <v>369</v>
+        <v>359</v>
       </c>
     </row>
     <row r="34">
@@ -32394,7 +32394,7 @@
         <v>401</v>
       </c>
       <c r="V34" t="n">
-        <v>2085</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="35">
@@ -32464,7 +32464,7 @@
         <v>286</v>
       </c>
       <c r="V35" t="n">
-        <v>1398</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="36">
@@ -32534,7 +32534,7 @@
         <v>70</v>
       </c>
       <c r="V36" t="n">
-        <v>427</v>
+        <v>410</v>
       </c>
     </row>
     <row r="37">
@@ -32604,7 +32604,7 @@
         <v>174</v>
       </c>
       <c r="V37" t="n">
-        <v>1183</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="38">
@@ -32674,7 +32674,7 @@
         <v>62</v>
       </c>
       <c r="V38" t="n">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39">
@@ -32744,7 +32744,7 @@
         <v>178</v>
       </c>
       <c r="V39" t="n">
-        <v>830</v>
+        <v>802</v>
       </c>
     </row>
     <row r="40">
@@ -32814,7 +32814,7 @@
         <v>577</v>
       </c>
       <c r="V40" t="n">
-        <v>2849</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="41">
@@ -32884,7 +32884,7 @@
         <v>558</v>
       </c>
       <c r="V41" t="n">
-        <v>2650</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="42">
@@ -32954,7 +32954,7 @@
         <v>59</v>
       </c>
       <c r="V42" t="n">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="43">
@@ -33024,7 +33024,7 @@
         <v>309</v>
       </c>
       <c r="V43" t="n">
-        <v>1267</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="44">
@@ -33094,7 +33094,7 @@
         <v>45</v>
       </c>
       <c r="V44" t="n">
-        <v>326</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45">
@@ -33164,7 +33164,7 @@
         <v>15</v>
       </c>
       <c r="V45" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46">
@@ -33234,7 +33234,7 @@
         <v>168</v>
       </c>
       <c r="V46" t="n">
-        <v>865</v>
+        <v>834</v>
       </c>
     </row>
     <row r="47">
@@ -33304,7 +33304,7 @@
         <v>181</v>
       </c>
       <c r="V47" t="n">
-        <v>952</v>
+        <v>920</v>
       </c>
     </row>
     <row r="48">
@@ -33374,7 +33374,7 @@
         <v>136</v>
       </c>
       <c r="V48" t="n">
-        <v>806</v>
+        <v>777</v>
       </c>
     </row>
     <row r="49">
@@ -33444,7 +33444,7 @@
         <v>91</v>
       </c>
       <c r="V49" t="n">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="50">
@@ -33514,7 +33514,7 @@
         <v>384</v>
       </c>
       <c r="V50" t="n">
-        <v>2025</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="51">
@@ -33584,7 +33584,7 @@
         <v>48</v>
       </c>
       <c r="V51" t="n">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52">
@@ -33654,7 +33654,7 @@
         <v>409</v>
       </c>
       <c r="V52" t="n">
-        <v>2147</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="53">
@@ -33724,7 +33724,7 @@
         <v>231</v>
       </c>
       <c r="V53" t="n">
-        <v>1142</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="54">
@@ -33794,7 +33794,7 @@
         <v>122</v>
       </c>
       <c r="V54" t="n">
-        <v>616</v>
+        <v>597</v>
       </c>
     </row>
     <row r="55">
@@ -33864,7 +33864,7 @@
         <v>18</v>
       </c>
       <c r="V55" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56">
@@ -33934,7 +33934,7 @@
         <v>3158</v>
       </c>
       <c r="V56" t="n">
-        <v>11921</v>
+        <v>11509</v>
       </c>
     </row>
     <row r="57">
@@ -34004,7 +34004,7 @@
         <v>293</v>
       </c>
       <c r="V57" t="n">
-        <v>1210</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="58">
@@ -34074,7 +34074,7 @@
         <v>1584</v>
       </c>
       <c r="V58" t="n">
-        <v>8342</v>
+        <v>8092</v>
       </c>
     </row>
     <row r="59">
@@ -34144,7 +34144,7 @@
         <v>1743</v>
       </c>
       <c r="V59" t="n">
-        <v>8203</v>
+        <v>7908</v>
       </c>
     </row>
     <row r="60">
@@ -34214,7 +34214,7 @@
         <v>636</v>
       </c>
       <c r="V60" t="n">
-        <v>3520</v>
+        <v>3398</v>
       </c>
     </row>
     <row r="61">
@@ -34284,7 +34284,7 @@
         <v>1212</v>
       </c>
       <c r="V61" t="n">
-        <v>6247</v>
+        <v>6041</v>
       </c>
     </row>
     <row r="62">
@@ -34354,7 +34354,7 @@
         <v>3726</v>
       </c>
       <c r="V62" t="n">
-        <v>16219</v>
+        <v>15626</v>
       </c>
     </row>
     <row r="63">
@@ -34424,7 +34424,7 @@
         <v>3469</v>
       </c>
       <c r="V63" t="n">
-        <v>16395</v>
+        <v>15863</v>
       </c>
     </row>
     <row r="64">
@@ -34494,7 +34494,7 @@
         <v>958</v>
       </c>
       <c r="V64" t="n">
-        <v>4688</v>
+        <v>4542</v>
       </c>
     </row>
     <row r="65">
@@ -34564,7 +34564,7 @@
         <v>473</v>
       </c>
       <c r="V65" t="n">
-        <v>2141</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="66">
@@ -34634,7 +34634,7 @@
         <v>4338</v>
       </c>
       <c r="V66" t="n">
-        <v>11990</v>
+        <v>11269</v>
       </c>
     </row>
     <row r="67">
@@ -34704,7 +34704,7 @@
         <v>258</v>
       </c>
       <c r="V67" t="n">
-        <v>1079</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="68">
@@ -34774,7 +34774,7 @@
         <v>1</v>
       </c>
       <c r="V68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -34844,7 +34844,7 @@
         <v>4670</v>
       </c>
       <c r="V69" t="n">
-        <v>12863</v>
+        <v>12102</v>
       </c>
     </row>
     <row r="70">
@@ -34984,7 +34984,7 @@
         <v>22</v>
       </c>
       <c r="V71" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72">
@@ -35194,7 +35194,7 @@
         <v>2</v>
       </c>
       <c r="V74" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="75">
@@ -35264,7 +35264,7 @@
         <v>1304</v>
       </c>
       <c r="V75" t="n">
-        <v>9003</v>
+        <v>8799</v>
       </c>
     </row>
     <row r="76">
@@ -35334,7 +35334,7 @@
         <v>70</v>
       </c>
       <c r="V76" t="n">
-        <v>1277</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="77">
@@ -35404,7 +35404,7 @@
         <v>313</v>
       </c>
       <c r="V77" t="n">
-        <v>3062</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="78">
@@ -35474,7 +35474,7 @@
         <v>10</v>
       </c>
       <c r="V78" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79">
@@ -35544,7 +35544,7 @@
         <v>29</v>
       </c>
       <c r="V79" t="n">
-        <v>1364</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="80">
@@ -35614,7 +35614,7 @@
         <v>443</v>
       </c>
       <c r="V80" t="n">
-        <v>4048</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="81">
@@ -35684,7 +35684,7 @@
         <v>554</v>
       </c>
       <c r="V81" t="n">
-        <v>2950</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="82">
@@ -35754,7 +35754,7 @@
         <v>642</v>
       </c>
       <c r="V82" t="n">
-        <v>4015</v>
+        <v>3802</v>
       </c>
     </row>
     <row r="83">
@@ -35824,7 +35824,7 @@
         <v>5568</v>
       </c>
       <c r="V83" t="n">
-        <v>4683</v>
+        <v>4522</v>
       </c>
     </row>
     <row r="84">
@@ -35894,7 +35894,7 @@
         <v>1310</v>
       </c>
       <c r="V84" t="n">
-        <v>566</v>
+        <v>514</v>
       </c>
     </row>
     <row r="85">
@@ -35964,7 +35964,7 @@
         <v>55</v>
       </c>
       <c r="V85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
@@ -36034,7 +36034,7 @@
         <v>58</v>
       </c>
       <c r="V86" t="n">
-        <v>280</v>
+        <v>263</v>
       </c>
     </row>
     <row r="87">
@@ -36104,7 +36104,7 @@
         <v>21</v>
       </c>
       <c r="V87" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88">
@@ -36314,7 +36314,7 @@
         <v>8527</v>
       </c>
       <c r="V90" t="n">
-        <v>38763</v>
+        <v>37469</v>
       </c>
     </row>
     <row r="91">
@@ -36384,7 +36384,7 @@
         <v>3</v>
       </c>
       <c r="V91" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92">
@@ -36454,7 +36454,7 @@
         <v>3</v>
       </c>
       <c r="V92" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93">
@@ -36524,7 +36524,7 @@
         <v>98</v>
       </c>
       <c r="V93" t="n">
-        <v>804</v>
+        <v>771</v>
       </c>
     </row>
     <row r="94">
@@ -36664,7 +36664,7 @@
         <v>22</v>
       </c>
       <c r="V95" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="96">
@@ -36734,7 +36734,7 @@
         <v>6</v>
       </c>
       <c r="V96" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="97">
@@ -36874,7 +36874,7 @@
         <v>16</v>
       </c>
       <c r="V98" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="99">
@@ -37014,7 +37014,7 @@
         <v>25</v>
       </c>
       <c r="V100" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="101">
@@ -37084,7 +37084,7 @@
         <v>51</v>
       </c>
       <c r="V101" t="n">
-        <v>227</v>
+        <v>205</v>
       </c>
     </row>
     <row r="102">
@@ -37154,7 +37154,7 @@
         <v>12</v>
       </c>
       <c r="V102" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="103">
@@ -37294,7 +37294,7 @@
         <v>114</v>
       </c>
       <c r="V104" t="n">
-        <v>294</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/results/enrichment_OR_by_protein_class.xlsx
+++ b/results/enrichment_OR_by_protein_class.xlsx
@@ -5412,7 +5412,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>PI:HB_intra</t>
+          <t>Intra:HB_intra</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -5482,7 +5482,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>PI:SB_intra</t>
+          <t>Intra:SB_intra</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -5552,7 +5552,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>PI:DS_intra</t>
+          <t>Intra:DS_intra</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -5632,7 +5632,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>PI:NB_intra</t>
+          <t>Intra:NB_intra</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -7688,7 +7688,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>PPI:HB_inter</t>
+          <t>Inter:HB_inter</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -7758,7 +7758,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>PPI:SB_inter</t>
+          <t>Inter:SB_inter</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -7830,7 +7830,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>PPI:DS_inter</t>
+          <t>Inter:DS_inter</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -7886,7 +7886,7 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>PPI:NB_inter</t>
+          <t>Inter:NB_inter</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -12562,7 +12562,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>PI:HB_intra</t>
+          <t>Intra:HB_intra</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -12632,7 +12632,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>PI:SB_intra</t>
+          <t>Intra:SB_intra</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -12702,7 +12702,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>PI:DS_intra</t>
+          <t>Intra:DS_intra</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -12772,7 +12772,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>PI:NB_intra</t>
+          <t>Intra:NB_intra</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -15012,7 +15012,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>PPI:HB_inter</t>
+          <t>Inter:HB_inter</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -15082,7 +15082,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>PPI:SB_inter</t>
+          <t>Inter:SB_inter</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -15152,7 +15152,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>PPI:DS_inter</t>
+          <t>Inter:DS_inter</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -15222,7 +15222,7 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>PPI:NB_inter</t>
+          <t>Inter:NB_inter</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -19898,7 +19898,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>PI:HB_intra</t>
+          <t>Intra:HB_intra</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -19968,7 +19968,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>PI:SB_intra</t>
+          <t>Intra:SB_intra</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -20038,7 +20038,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>PI:DS_intra</t>
+          <t>Intra:DS_intra</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -20108,7 +20108,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>PI:NB_intra</t>
+          <t>Intra:NB_intra</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -22348,7 +22348,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>PPI:HB_inter</t>
+          <t>Inter:HB_inter</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -22418,7 +22418,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>PPI:SB_inter</t>
+          <t>Inter:SB_inter</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -22488,7 +22488,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>PPI:DS_inter</t>
+          <t>Inter:DS_inter</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -22558,7 +22558,7 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>PPI:NB_inter</t>
+          <t>Inter:NB_inter</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -27234,7 +27234,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>PI:HB_intra</t>
+          <t>Intra:HB_intra</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -27304,7 +27304,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>PI:SB_intra</t>
+          <t>Intra:SB_intra</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -27374,7 +27374,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>PI:DS_intra</t>
+          <t>Intra:DS_intra</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -27444,7 +27444,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>PI:NB_intra</t>
+          <t>Intra:NB_intra</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -29684,7 +29684,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>PPI:HB_inter</t>
+          <t>Inter:HB_inter</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -29754,7 +29754,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>PPI:SB_inter</t>
+          <t>Inter:SB_inter</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -29824,7 +29824,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>PPI:DS_inter</t>
+          <t>Inter:DS_inter</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -29894,7 +29894,7 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>PPI:NB_inter</t>
+          <t>Inter:NB_inter</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -34570,7 +34570,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>PI:HB_intra</t>
+          <t>Intra:HB_intra</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -34640,7 +34640,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>PI:SB_intra</t>
+          <t>Intra:SB_intra</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -34710,7 +34710,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>PI:DS_intra</t>
+          <t>Intra:DS_intra</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -34780,7 +34780,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>PI:NB_intra</t>
+          <t>Intra:NB_intra</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -37020,7 +37020,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>PPI:HB_inter</t>
+          <t>Inter:HB_inter</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -37090,7 +37090,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>PPI:SB_inter</t>
+          <t>Inter:SB_inter</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -37160,7 +37160,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>PPI:DS_inter</t>
+          <t>Inter:DS_inter</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -37230,7 +37230,7 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>PPI:NB_inter</t>
+          <t>Inter:NB_inter</t>
         </is>
       </c>
       <c r="B104" t="n">
